--- a/260513_Betonartikel/Results/Members_rc_rec_2.xlsx
+++ b/260513_Betonartikel/Results/Members_rc_rec_2.xlsx
@@ -900,76 +900,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3293938074329805</v>
+        <v>0.3354189693557738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3740842278905603</v>
+        <v>0.3784429462471306</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4177826803823887</v>
+        <v>0.4326905840510017</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4633538767188397</v>
+        <v>0.4662194205021523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3082268443163953</v>
+        <v>0.3100929757029407</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3477136262086474</v>
+        <v>0.3445589472704024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3819628199693083</v>
+        <v>0.3825005545803515</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4205890838810008</v>
+        <v>0.4218731112609591</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3408697665017533</v>
+        <v>0.3315503881231726</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3796912381615085</v>
+        <v>0.3781159454921432</v>
       </c>
       <c r="M5" t="n">
-        <v>0.423229651918234</v>
+        <v>0.4179093484104668</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4662935341824795</v>
+        <v>0.4648604399968322</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3183346729816215</v>
+        <v>0.3155559954830414</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3556350530808884</v>
+        <v>0.3554021383750871</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4012350055288814</v>
+        <v>0.3983134829052168</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4501392224325191</v>
+        <v>0.4413290265770735</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2961155049498828</v>
+        <v>0.3011478250907526</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3330324077056088</v>
+        <v>0.3322901514667294</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3760589167416343</v>
+        <v>0.3713014378889367</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4149816160737073</v>
+        <v>0.4123995377729053</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2949274402971205</v>
+        <v>0.2964739486646165</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3340616460499855</v>
+        <v>0.3324172347068447</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.377563643446294</v>
+        <v>0.3763998141236561</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4118848176296432</v>
+        <v>0.4234862012666542</v>
       </c>
     </row>
     <row r="6">
@@ -982,76 +982,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3293938074329805</v>
+        <v>0.3354189693557738</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3740842278905603</v>
+        <v>0.3784429462471306</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4177826803823887</v>
+        <v>0.4326905840510017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4633538767188397</v>
+        <v>0.4662194205021523</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3082268443163953</v>
+        <v>0.3100929757029407</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3477136262086474</v>
+        <v>0.3445589472704024</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3819628199693083</v>
+        <v>0.3825005545803515</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4205890838810008</v>
+        <v>0.4218731112609591</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3408697665017533</v>
+        <v>0.3315503881231726</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3796912381615085</v>
+        <v>0.3781159454921432</v>
       </c>
       <c r="M6" t="n">
-        <v>0.423229651918234</v>
+        <v>0.4179093484104668</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4662935341824795</v>
+        <v>0.4648604399968322</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3183346729816215</v>
+        <v>0.3155559954830414</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3556350530808884</v>
+        <v>0.3554021383750871</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4012350055288814</v>
+        <v>0.3983134829052168</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4501392224325191</v>
+        <v>0.4413290265770735</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2961155049498828</v>
+        <v>0.3011478250907526</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3330324077056088</v>
+        <v>0.3322901514667294</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3760589167416343</v>
+        <v>0.3713014378889367</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4149816160737073</v>
+        <v>0.4123995377729053</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2949274402971205</v>
+        <v>0.2964739486646165</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3340616460499855</v>
+        <v>0.3324172347068447</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.377563643446294</v>
+        <v>0.3763998141236561</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4118848176296432</v>
+        <v>0.4234862012666542</v>
       </c>
     </row>
     <row r="7">
@@ -1064,76 +1064,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002978276705027625</v>
+        <v>0.003144717332866396</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004362414695142025</v>
+        <v>0.00451668703116618</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006076731529567955</v>
+        <v>0.006750735422812662</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008290050131837274</v>
+        <v>0.008444809062789081</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002440226469739529</v>
+        <v>0.002484817744610764</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003503352880001391</v>
+        <v>0.003408861445562933</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004643891100644258</v>
+        <v>0.004663532003422298</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00620001505326843</v>
+        <v>0.006256973151574923</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003300533942035324</v>
+        <v>0.003037157932734394</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004561529418562094</v>
+        <v>0.004504988959451988</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006317525675284118</v>
+        <v>0.006082260439939623</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008448837050583444</v>
+        <v>0.008371176923552852</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002688255775249523</v>
+        <v>0.0026184727713386</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003748283538007629</v>
+        <v>0.003740923813163202</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005382886235327406</v>
+        <v>0.00526615668378078</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007600800316445799</v>
+        <v>0.00716318604290063</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002163725674480431</v>
+        <v>0.002275925003246717</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003078068251953744</v>
+        <v>0.003057533070112978</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004431864012957847</v>
+        <v>0.004265781899777239</v>
       </c>
       <c r="V7" t="n">
-        <v>0.005955323075470632</v>
+        <v>0.005844848565513702</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002137786344552874</v>
+        <v>0.002171592669511161</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003106694897360564</v>
+        <v>0.003061042441339781</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.004485276894086753</v>
+        <v>0.004443927395071083</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00582299082063631</v>
+        <v>0.006329021134607402</v>
       </c>
     </row>
     <row r="8">
@@ -3552,76 +3552,76 @@
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02631538674967577</v>
+        <v>0.02563422911930011</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0279720913183651</v>
+        <v>0.02751690696874891</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02985598454340249</v>
+        <v>0.02846777801523241</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03166528531945153</v>
+        <v>0.03140510414776462</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02904002691965342</v>
+        <v>0.02877984711946835</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03105811965033422</v>
+        <v>0.03147637165208264</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03385101941020925</v>
+        <v>0.03378518919706471</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03615193544405943</v>
+        <v>0.03599776688406669</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02624112215451354</v>
+        <v>0.0273320538780705</v>
       </c>
       <c r="L35" t="n">
-        <v>0.02869136024210286</v>
+        <v>0.02885949802395869</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0307239459591958</v>
+        <v>0.0312591610576993</v>
       </c>
       <c r="N35" t="n">
-        <v>0.03288091191783573</v>
+        <v>0.03301818557161434</v>
       </c>
       <c r="O35" t="n">
-        <v>0.02900560100009045</v>
+        <v>0.02938931219443637</v>
       </c>
       <c r="P35" t="n">
-        <v>0.03154729620110175</v>
+        <v>0.03153623573405993</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.03308150577833822</v>
+        <v>0.03342398182562342</v>
       </c>
       <c r="R35" t="n">
-        <v>0.03450017371307366</v>
+        <v>0.0354376178655659</v>
       </c>
       <c r="S35" t="n">
-        <v>0.03088474591889633</v>
+        <v>0.03008730848310669</v>
       </c>
       <c r="T35" t="n">
-        <v>0.03311048646395695</v>
+        <v>0.03322636394260526</v>
       </c>
       <c r="U35" t="n">
-        <v>0.03462000241874679</v>
+        <v>0.03526695756485747</v>
       </c>
       <c r="V35" t="n">
-        <v>0.03684452008659849</v>
+        <v>0.03716897005191668</v>
       </c>
       <c r="W35" t="n">
-        <v>0.03111945718481901</v>
+        <v>0.03082332573517139</v>
       </c>
       <c r="X35" t="n">
-        <v>0.03295735514874917</v>
+        <v>0.03323312149774763</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.03442054137674962</v>
+        <v>0.03457460205152302</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.03723491461940474</v>
+        <v>0.03580603690447501</v>
       </c>
     </row>
     <row r="36">
@@ -3716,76 +3716,76 @@
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>0.009295294523639711</v>
+        <v>0.009365232275883987</v>
       </c>
       <c r="D37" t="n">
-        <v>0.009852216991102126</v>
+        <v>0.009900480397671623</v>
       </c>
       <c r="E37" t="n">
-        <v>0.010370511395443</v>
+        <v>0.01052818738589454</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01088430446714975</v>
+        <v>0.01091344841098406</v>
       </c>
       <c r="G37" t="n">
-        <v>0.009048870390386954</v>
+        <v>0.009070638678665055</v>
       </c>
       <c r="H37" t="n">
-        <v>0.009558345433342098</v>
+        <v>0.009523070797481948</v>
       </c>
       <c r="I37" t="n">
-        <v>0.009987453885684708</v>
+        <v>0.009993254016598365</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01044483435370553</v>
+        <v>0.01045813139098298</v>
       </c>
       <c r="K37" t="n">
-        <v>0.008936025797838606</v>
+        <v>0.008834461649713103</v>
       </c>
       <c r="L37" t="n">
-        <v>0.009396325203518166</v>
+        <v>0.009379903023552079</v>
       </c>
       <c r="M37" t="n">
-        <v>0.009882997659270825</v>
+        <v>0.0098298259987588</v>
       </c>
       <c r="N37" t="n">
-        <v>0.01034317264283154</v>
+        <v>0.01032944342422559</v>
       </c>
       <c r="O37" t="n">
-        <v>0.008689759646229886</v>
+        <v>0.008659341268099151</v>
       </c>
       <c r="P37" t="n">
-        <v>0.009144880635906601</v>
+        <v>0.009142141494633995</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.00966248331819014</v>
+        <v>0.009633060804271964</v>
       </c>
       <c r="R37" t="n">
-        <v>0.01018789662633395</v>
+        <v>0.01010266185826153</v>
       </c>
       <c r="S37" t="n">
-        <v>0.008907990373204352</v>
+        <v>0.008966451755776915</v>
       </c>
       <c r="T37" t="n">
-        <v>0.009394152345506838</v>
+        <v>0.009385889704630142</v>
       </c>
       <c r="U37" t="n">
-        <v>0.009923929259141352</v>
+        <v>0.009872703730073538</v>
       </c>
       <c r="V37" t="n">
-        <v>0.01038673047414768</v>
+        <v>0.01035992241418545</v>
       </c>
       <c r="W37" t="n">
-        <v>0.008894549414505806</v>
+        <v>0.008912123485849939</v>
       </c>
       <c r="X37" t="n">
-        <v>0.009405660674678412</v>
+        <v>0.009387515750990894</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.00994012543695421</v>
+        <v>0.00992759881438705</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.01035458033731428</v>
+        <v>0.01047482914516271</v>
       </c>
     </row>
     <row r="38">
@@ -3880,76 +3880,76 @@
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>0.009295294523639711</v>
+        <v>0.009365232275883987</v>
       </c>
       <c r="D39" t="n">
-        <v>0.009852216991102126</v>
+        <v>0.009900480397671623</v>
       </c>
       <c r="E39" t="n">
-        <v>0.010370511395443</v>
+        <v>0.01052818738589454</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01088430446714975</v>
+        <v>0.01091344841098406</v>
       </c>
       <c r="G39" t="n">
-        <v>0.009048870390386954</v>
+        <v>0.009070638678665055</v>
       </c>
       <c r="H39" t="n">
-        <v>0.009558345433342098</v>
+        <v>0.009523070797481948</v>
       </c>
       <c r="I39" t="n">
-        <v>0.009987453885684708</v>
+        <v>0.009993254016598365</v>
       </c>
       <c r="J39" t="n">
-        <v>0.01044483435370553</v>
+        <v>0.01045813139098298</v>
       </c>
       <c r="K39" t="n">
-        <v>0.008936025797838606</v>
+        <v>0.008834461649713103</v>
       </c>
       <c r="L39" t="n">
-        <v>0.009396325203518166</v>
+        <v>0.009379903023552079</v>
       </c>
       <c r="M39" t="n">
-        <v>0.009882997659270825</v>
+        <v>0.0098298259987588</v>
       </c>
       <c r="N39" t="n">
-        <v>0.01034317264283154</v>
+        <v>0.01032944342422559</v>
       </c>
       <c r="O39" t="n">
-        <v>0.008689759646229886</v>
+        <v>0.008659341268099151</v>
       </c>
       <c r="P39" t="n">
-        <v>0.009144880635906601</v>
+        <v>0.009142141494633995</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.00966248331819014</v>
+        <v>0.009633060804271964</v>
       </c>
       <c r="R39" t="n">
-        <v>0.01018789662633395</v>
+        <v>0.01010266185826153</v>
       </c>
       <c r="S39" t="n">
-        <v>0.008907990373204352</v>
+        <v>0.008966451755776915</v>
       </c>
       <c r="T39" t="n">
-        <v>0.009394152345506838</v>
+        <v>0.009385889704630142</v>
       </c>
       <c r="U39" t="n">
-        <v>0.009923929259141352</v>
+        <v>0.009872703730073538</v>
       </c>
       <c r="V39" t="n">
-        <v>0.01038673047414768</v>
+        <v>0.01035992241418545</v>
       </c>
       <c r="W39" t="n">
-        <v>0.008894549414505806</v>
+        <v>0.008912123485849939</v>
       </c>
       <c r="X39" t="n">
-        <v>0.009405660674678412</v>
+        <v>0.009387515750990894</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.00994012543695421</v>
+        <v>0.00992759881438705</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.01035458033731428</v>
+        <v>0.01047482914516271</v>
       </c>
     </row>
     <row r="40">
@@ -4044,76 +4044,76 @@
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>0.009295294523639711</v>
+        <v>0.009365232275883987</v>
       </c>
       <c r="D41" t="n">
-        <v>0.009852216991102126</v>
+        <v>0.009900480397671623</v>
       </c>
       <c r="E41" t="n">
-        <v>0.010370511395443</v>
+        <v>0.01052818738589454</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01088430446714975</v>
+        <v>0.01091344841098406</v>
       </c>
       <c r="G41" t="n">
-        <v>0.009048870390386954</v>
+        <v>0.009070638678665055</v>
       </c>
       <c r="H41" t="n">
-        <v>0.009558345433342098</v>
+        <v>0.009523070797481948</v>
       </c>
       <c r="I41" t="n">
-        <v>0.009987453885684708</v>
+        <v>0.009993254016598365</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01044483435370553</v>
+        <v>0.01045813139098298</v>
       </c>
       <c r="K41" t="n">
-        <v>0.008936025797838606</v>
+        <v>0.008834461649713103</v>
       </c>
       <c r="L41" t="n">
-        <v>0.009396325203518166</v>
+        <v>0.009379903023552079</v>
       </c>
       <c r="M41" t="n">
-        <v>0.009882997659270825</v>
+        <v>0.0098298259987588</v>
       </c>
       <c r="N41" t="n">
-        <v>0.01034317264283154</v>
+        <v>0.01032944342422559</v>
       </c>
       <c r="O41" t="n">
-        <v>0.008689759646229886</v>
+        <v>0.008659341268099151</v>
       </c>
       <c r="P41" t="n">
-        <v>0.009144880635906601</v>
+        <v>0.009142141494633995</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.00966248331819014</v>
+        <v>0.009633060804271964</v>
       </c>
       <c r="R41" t="n">
-        <v>0.01018789662633395</v>
+        <v>0.01010266185826153</v>
       </c>
       <c r="S41" t="n">
-        <v>0.008907990373204352</v>
+        <v>0.008966451755776915</v>
       </c>
       <c r="T41" t="n">
-        <v>0.009394152345506838</v>
+        <v>0.009385889704630142</v>
       </c>
       <c r="U41" t="n">
-        <v>0.009923929259141352</v>
+        <v>0.009872703730073538</v>
       </c>
       <c r="V41" t="n">
-        <v>0.01038673047414768</v>
+        <v>0.01035992241418545</v>
       </c>
       <c r="W41" t="n">
-        <v>0.008894549414505806</v>
+        <v>0.008912123485849939</v>
       </c>
       <c r="X41" t="n">
-        <v>0.009405660674678412</v>
+        <v>0.009387515750990894</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.00994012543695421</v>
+        <v>0.00992759881438705</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.01035458033731428</v>
+        <v>0.01047482914516271</v>
       </c>
     </row>
     <row r="42">
@@ -4454,76 +4454,76 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>52441.80218134445</v>
+        <v>54377.84441844994</v>
       </c>
       <c r="D46" t="n">
-        <v>67637.18795229704</v>
+        <v>69222.54738936748</v>
       </c>
       <c r="E46" t="n">
-        <v>84362.14454662171</v>
+        <v>90490.21840442521</v>
       </c>
       <c r="F46" t="n">
-        <v>103770.1272840159</v>
+        <v>105057.598225792</v>
       </c>
       <c r="G46" t="n">
-        <v>45918.4973193343</v>
+        <v>46476.19923048055</v>
       </c>
       <c r="H46" t="n">
-        <v>58437.30349473069</v>
+        <v>57381.75293630918</v>
       </c>
       <c r="I46" t="n">
-        <v>70516.20465547135</v>
+        <v>70714.89255623361</v>
       </c>
       <c r="J46" t="n">
-        <v>85499.33578193211</v>
+        <v>86022.17896908411</v>
       </c>
       <c r="K46" t="n">
-        <v>50349.95234314924</v>
+        <v>47634.45260800476</v>
       </c>
       <c r="L46" t="n">
-        <v>62471.68907920172</v>
+        <v>61954.38956868086</v>
       </c>
       <c r="M46" t="n">
-        <v>77620.11324722611</v>
+        <v>75680.89684517309</v>
       </c>
       <c r="N46" t="n">
-        <v>94219.5193421678</v>
+        <v>93641.26575875432</v>
       </c>
       <c r="O46" t="n">
-        <v>43912.68440967023</v>
+        <v>43149.42072362707</v>
       </c>
       <c r="P46" t="n">
-        <v>54806.39275793341</v>
+        <v>54734.62798335332</v>
       </c>
       <c r="Q46" t="n">
-        <v>69762.12952009663</v>
+        <v>68749.90662110325</v>
       </c>
       <c r="R46" t="n">
-        <v>87804.30514793292</v>
+        <v>84400.90086976913</v>
       </c>
       <c r="S46" t="n">
-        <v>42380.78959799997</v>
+        <v>43833.50606916374</v>
       </c>
       <c r="T46" t="n">
-        <v>53606.78254806084</v>
+        <v>53368.09330152794</v>
       </c>
       <c r="U46" t="n">
-        <v>68353.14928276418</v>
+        <v>66634.63292622274</v>
       </c>
       <c r="V46" t="n">
-        <v>83234.70847825379</v>
+        <v>82202.13306506452</v>
       </c>
       <c r="W46" t="n">
-        <v>42041.39426943559</v>
+        <v>42483.45441444834</v>
       </c>
       <c r="X46" t="n">
-        <v>53938.63862478581</v>
+        <v>53408.92199957031</v>
       </c>
       <c r="Y46" t="n">
-        <v>68901.24734534611</v>
+        <v>68477.1297016227</v>
       </c>
       <c r="Z46" t="n">
-        <v>81997.06644700551</v>
+        <v>86681.27195390956</v>
       </c>
     </row>
     <row r="47">
@@ -4536,76 +4536,76 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>-52441.80218134445</v>
+        <v>-54377.84441844994</v>
       </c>
       <c r="D47" t="n">
-        <v>-67637.18795229704</v>
+        <v>-69222.54738936748</v>
       </c>
       <c r="E47" t="n">
-        <v>-84362.14454662171</v>
+        <v>-90490.21840442521</v>
       </c>
       <c r="F47" t="n">
-        <v>-103770.1272840159</v>
+        <v>-105057.598225792</v>
       </c>
       <c r="G47" t="n">
-        <v>-45918.4973193343</v>
+        <v>-46476.19923048055</v>
       </c>
       <c r="H47" t="n">
-        <v>-58437.30349473069</v>
+        <v>-57381.75293630918</v>
       </c>
       <c r="I47" t="n">
-        <v>-70516.20465547135</v>
+        <v>-70714.89255623361</v>
       </c>
       <c r="J47" t="n">
-        <v>-85499.33578193211</v>
+        <v>-86022.17896908411</v>
       </c>
       <c r="K47" t="n">
-        <v>-50349.95234314924</v>
+        <v>-47634.45260800476</v>
       </c>
       <c r="L47" t="n">
-        <v>-62471.68907920172</v>
+        <v>-61954.38956868086</v>
       </c>
       <c r="M47" t="n">
-        <v>-77620.11324722611</v>
+        <v>-75680.89684517309</v>
       </c>
       <c r="N47" t="n">
-        <v>-94219.5193421678</v>
+        <v>-93641.26575875432</v>
       </c>
       <c r="O47" t="n">
-        <v>-43912.68440967023</v>
+        <v>-43149.42072362707</v>
       </c>
       <c r="P47" t="n">
-        <v>-54806.39275793341</v>
+        <v>-54734.62798335332</v>
       </c>
       <c r="Q47" t="n">
-        <v>-69762.12952009663</v>
+        <v>-68749.90662110325</v>
       </c>
       <c r="R47" t="n">
-        <v>-87804.30514793292</v>
+        <v>-84400.90086976913</v>
       </c>
       <c r="S47" t="n">
-        <v>-42380.78959799997</v>
+        <v>-43833.50606916374</v>
       </c>
       <c r="T47" t="n">
-        <v>-53606.78254806084</v>
+        <v>-53368.09330152794</v>
       </c>
       <c r="U47" t="n">
-        <v>-68353.14928276418</v>
+        <v>-66634.63292622274</v>
       </c>
       <c r="V47" t="n">
-        <v>-83234.70847825379</v>
+        <v>-82202.13306506452</v>
       </c>
       <c r="W47" t="n">
-        <v>-42041.39426943559</v>
+        <v>-42483.45441444834</v>
       </c>
       <c r="X47" t="n">
-        <v>-53938.63862478581</v>
+        <v>-53408.92199957031</v>
       </c>
       <c r="Y47" t="n">
-        <v>-68901.24734534611</v>
+        <v>-68477.1297016227</v>
       </c>
       <c r="Z47" t="n">
-        <v>-81997.06644700551</v>
+        <v>-86681.27195390956</v>
       </c>
     </row>
     <row r="48">
@@ -4618,76 +4618,76 @@
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2962361140581425</v>
+        <v>0.3026018547961237</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3400981822313777</v>
+        <v>0.3446844927627561</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3828546881106875</v>
+        <v>0.3984566950433855</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4275212340591139</v>
+        <v>0.4305168684282699</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2737068308565686</v>
+        <v>0.2757030521432065</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3121845663834802</v>
+        <v>0.3088207614443611</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3450373102642036</v>
+        <v>0.3456079599818191</v>
       </c>
       <c r="J48" t="n">
-        <v>0.382513116158971</v>
+        <v>0.3838742278189258</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3077492054244965</v>
+        <v>0.2978843611841373</v>
       </c>
       <c r="L48" t="n">
-        <v>0.345345558040457</v>
+        <v>0.3436861964801638</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3878676789386361</v>
+        <v>0.3822797678816172</v>
       </c>
       <c r="N48" t="n">
-        <v>0.4298530782235617</v>
+        <v>0.428351347211025</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2838318724815763</v>
+        <v>0.2808613393858232</v>
       </c>
       <c r="P48" t="n">
-        <v>0.3198614049803375</v>
+        <v>0.3196340205080571</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.3646942526397122</v>
+        <v>0.361601491992405</v>
       </c>
       <c r="R48" t="n">
-        <v>0.4128891355759822</v>
+        <v>0.4036102176442905</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2606731319904346</v>
+        <v>0.2661041708491992</v>
       </c>
       <c r="T48" t="n">
-        <v>0.2964771644736303</v>
+        <v>0.2956769694954268</v>
       </c>
       <c r="U48" t="n">
-        <v>0.3387489155322609</v>
+        <v>0.3336679591065079</v>
       </c>
       <c r="V48" t="n">
-        <v>0.376559356030408</v>
+        <v>0.3738150527469469</v>
       </c>
       <c r="W48" t="n">
-        <v>0.259367711704711</v>
+        <v>0.2610622857970308</v>
       </c>
       <c r="X48" t="n">
-        <v>0.2975829684756109</v>
+        <v>0.2958006739579709</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.3403533727579192</v>
+        <v>0.3391125130978946</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.3732673603199408</v>
+        <v>0.3855831828144167</v>
       </c>
     </row>
     <row r="49">
@@ -4700,76 +4700,76 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3053938074329804</v>
+        <v>0.3114189693557738</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3500842278905603</v>
+        <v>0.3544429462471306</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3937826803823887</v>
+        <v>0.4086905840510017</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4393538767188396</v>
+        <v>0.4422194205021522</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2842268443163953</v>
+        <v>0.2860929757029407</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3237136262086474</v>
+        <v>0.3205589472704024</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3579628199693083</v>
+        <v>0.3585005545803515</v>
       </c>
       <c r="J49" t="n">
-        <v>0.3965890838810008</v>
+        <v>0.3978731112609591</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3168697665017532</v>
+        <v>0.3075503881231725</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3556912381615084</v>
+        <v>0.3541159454921431</v>
       </c>
       <c r="M49" t="n">
-        <v>0.399229651918234</v>
+        <v>0.3939093484104668</v>
       </c>
       <c r="N49" t="n">
-        <v>0.4422935341824795</v>
+        <v>0.4408604399968322</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2943346729816215</v>
+        <v>0.2915559954830414</v>
       </c>
       <c r="P49" t="n">
-        <v>0.3316350530808884</v>
+        <v>0.3314021383750871</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.3772350055288813</v>
+        <v>0.3743134829052168</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4261392224325191</v>
+        <v>0.4173290265770734</v>
       </c>
       <c r="S49" t="n">
-        <v>0.2721155049498828</v>
+        <v>0.2771478250907525</v>
       </c>
       <c r="T49" t="n">
-        <v>0.3090324077056088</v>
+        <v>0.3082901514667294</v>
       </c>
       <c r="U49" t="n">
-        <v>0.3520589167416343</v>
+        <v>0.3473014378889366</v>
       </c>
       <c r="V49" t="n">
-        <v>0.3909816160737072</v>
+        <v>0.3883995377729053</v>
       </c>
       <c r="W49" t="n">
-        <v>0.2709274402971205</v>
+        <v>0.2724739486646165</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3100616460499855</v>
+        <v>0.3084172347068447</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.353563643446294</v>
+        <v>0.3523998141236561</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.3878848176296432</v>
+        <v>0.3994862012666542</v>
       </c>
     </row>
     <row r="50">
@@ -4782,76 +4782,76 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>404879.527556517</v>
+        <v>396726.0583148649</v>
       </c>
       <c r="D50" t="n">
-        <v>526474.2568711982</v>
+        <v>519862.6702547199</v>
       </c>
       <c r="E50" t="n">
-        <v>673958.8915027386</v>
+        <v>650027.9862777528</v>
       </c>
       <c r="F50" t="n">
-        <v>845616.2221998208</v>
+        <v>840600.0986154331</v>
       </c>
       <c r="G50" t="n">
-        <v>433328.5083086477</v>
+        <v>430977.0590830183</v>
       </c>
       <c r="H50" t="n">
-        <v>564985.4135139118</v>
+        <v>569360.4557847456</v>
       </c>
       <c r="I50" t="n">
-        <v>729953.2440840149</v>
+        <v>729258.2288829852</v>
       </c>
       <c r="J50" t="n">
-        <v>916786.0340361805</v>
+        <v>914866.2966341609</v>
       </c>
       <c r="K50" t="n">
-        <v>408706.8218225961</v>
+        <v>419831.0169702037</v>
       </c>
       <c r="L50" t="n">
-        <v>541824.7896996001</v>
+        <v>543794.5853549308</v>
       </c>
       <c r="M50" t="n">
-        <v>694966.6932580675</v>
+        <v>701920.4310507884</v>
       </c>
       <c r="N50" t="n">
-        <v>876247.7630182371</v>
+        <v>878319.0667608377</v>
       </c>
       <c r="O50" t="n">
-        <v>433570.260271913</v>
+        <v>436267.4715321635</v>
       </c>
       <c r="P50" t="n">
-        <v>570701.0560184473</v>
+        <v>569894.0237237698</v>
       </c>
       <c r="Q50" t="n">
-        <v>722384.4058896245</v>
+        <v>725597.0595904624</v>
       </c>
       <c r="R50" t="n">
-        <v>898519.1904771643</v>
+        <v>908683.2934125016</v>
       </c>
       <c r="S50" t="n">
-        <v>448165.6532893544</v>
+        <v>442216.3114779947</v>
       </c>
       <c r="T50" t="n">
-        <v>584214.5001320299</v>
+        <v>585200.2233503199</v>
       </c>
       <c r="U50" t="n">
-        <v>738159.9011589973</v>
+        <v>744333.7600377325</v>
       </c>
       <c r="V50" t="n">
-        <v>924957.7307273705</v>
+        <v>928390.2658828365</v>
       </c>
       <c r="W50" t="n">
-        <v>450299.3205390419</v>
+        <v>447693.1336600067</v>
       </c>
       <c r="X50" t="n">
-        <v>582981.2962962496</v>
+        <v>585685.0456400616</v>
       </c>
       <c r="Y50" t="n">
-        <v>736120.0242327541</v>
+        <v>737701.16585042</v>
       </c>
       <c r="Z50" t="n">
-        <v>929077.4352921734</v>
+        <v>912421.4692547994</v>
       </c>
     </row>
     <row r="51">
@@ -4864,76 +4864,76 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09273450948280522</v>
+        <v>0.08799589004583475</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1047783945297833</v>
+        <v>0.1013960638010476</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1193671045291825</v>
+        <v>0.1085248030123945</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1342729949954946</v>
+        <v>0.1320755235377293</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1129317073757659</v>
+        <v>0.1109171827437916</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1291731297779278</v>
+        <v>0.132675640830573</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1534494614527535</v>
+        <v>0.1528532142136028</v>
       </c>
       <c r="J51" t="n">
-        <v>0.175018908293244</v>
+        <v>0.1735293681072002</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1106542035973927</v>
+        <v>0.1200459871646144</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1322834118723479</v>
+        <v>0.1338383754805398</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1516900505523313</v>
+        <v>0.1570210030129069</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1737364000832936</v>
+        <v>0.1751900832824222</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1351969356392478</v>
+        <v>0.138797599647554</v>
       </c>
       <c r="P51" t="n">
-        <v>0.1599290648653987</v>
+        <v>0.1598169424157486</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.175862664703633</v>
+        <v>0.1795227465346928</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1912694788641667</v>
+        <v>0.2018051069139535</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1277350053809641</v>
+        <v>0.1212239811261862</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1468091039464543</v>
+        <v>0.147838484002667</v>
       </c>
       <c r="U51" t="n">
-        <v>0.1605003754550886</v>
+        <v>0.1665550692746184</v>
       </c>
       <c r="V51" t="n">
-        <v>0.18178903029244</v>
+        <v>0.1850047669843983</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1296838487284702</v>
+        <v>0.1272274599164011</v>
       </c>
       <c r="X51" t="n">
-        <v>0.1454543014243282</v>
+        <v>0.1478986246969797</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1586562767969177</v>
+        <v>0.1600796939086169</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.1856618140801874</v>
+        <v>0.1716857993377553</v>
       </c>
     </row>
     <row r="52">
@@ -4946,76 +4946,76 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.003625919320777684</v>
+        <v>0.003440639300792139</v>
       </c>
       <c r="D52" t="n">
-        <v>0.004096835226114528</v>
+        <v>0.00396458609462096</v>
       </c>
       <c r="E52" t="n">
-        <v>0.004667253787091037</v>
+        <v>0.004243319797784625</v>
       </c>
       <c r="F52" t="n">
-        <v>0.005250074104323838</v>
+        <v>0.005164152970325218</v>
       </c>
       <c r="G52" t="n">
-        <v>0.004415629758392447</v>
+        <v>0.00433686184528225</v>
       </c>
       <c r="H52" t="n">
-        <v>0.005050669374316978</v>
+        <v>0.005187617556475402</v>
       </c>
       <c r="I52" t="n">
-        <v>0.005999873942802659</v>
+        <v>0.005976560675751871</v>
       </c>
       <c r="J52" t="n">
-        <v>0.006843239314265839</v>
+        <v>0.006784998292991527</v>
       </c>
       <c r="K52" t="n">
-        <v>0.003605482800548379</v>
+        <v>0.003911498415113686</v>
       </c>
       <c r="L52" t="n">
-        <v>0.004310234503507336</v>
+        <v>0.004360900401074255</v>
       </c>
       <c r="M52" t="n">
-        <v>0.004942567480496794</v>
+        <v>0.005116267681503881</v>
       </c>
       <c r="N52" t="n">
-        <v>0.005660911036047317</v>
+        <v>0.005708276880285589</v>
       </c>
       <c r="O52" t="n">
-        <v>0.004405166819578824</v>
+        <v>0.0045224884551828</v>
       </c>
       <c r="P52" t="n">
-        <v>0.005211022030197571</v>
+        <v>0.005207368707046476</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.005730191824926709</v>
+        <v>0.005849449491255407</v>
       </c>
       <c r="R52" t="n">
-        <v>0.006232197186324099</v>
+        <v>0.006575483066946319</v>
       </c>
       <c r="S52" t="n">
-        <v>0.004994438710395695</v>
+        <v>0.004739857662033881</v>
       </c>
       <c r="T52" t="n">
-        <v>0.005740235964306365</v>
+        <v>0.005780484724504281</v>
       </c>
       <c r="U52" t="n">
-        <v>0.006275564680293967</v>
+        <v>0.006512303208637581</v>
       </c>
       <c r="V52" t="n">
-        <v>0.007107951084434402</v>
+        <v>0.007233686389089975</v>
       </c>
       <c r="W52" t="n">
-        <v>0.005070638485283185</v>
+        <v>0.004974593682731281</v>
       </c>
       <c r="X52" t="n">
-        <v>0.005687263185691234</v>
+        <v>0.005782836225651905</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.006203460422759482</v>
+        <v>0.006259116031826919</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.007259376930535326</v>
+        <v>0.006712914754106232</v>
       </c>
     </row>
     <row r="53">
@@ -5110,76 +5110,76 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>-43964.28625102848</v>
+        <v>-44842.13457257451</v>
       </c>
       <c r="D54" t="n">
-        <v>-50475.54870182832</v>
+        <v>-51110.60111078221</v>
       </c>
       <c r="E54" t="n">
-        <v>-56842.28434572726</v>
+        <v>-59014.32194089195</v>
       </c>
       <c r="F54" t="n">
-        <v>-63481.87324431937</v>
+        <v>-63899.37452191681</v>
       </c>
       <c r="G54" t="n">
-        <v>-40880.32215475624</v>
+        <v>-41152.21199381035</v>
       </c>
       <c r="H54" t="n">
-        <v>-46633.42981419283</v>
+        <v>-46173.80239729661</v>
       </c>
       <c r="I54" t="n">
-        <v>-51623.4363305924</v>
+        <v>-51701.78267742762</v>
       </c>
       <c r="J54" t="n">
-        <v>-57251.16905827211</v>
+        <v>-57438.24806042331</v>
       </c>
       <c r="K54" t="n">
-        <v>-45530.16148739998</v>
+        <v>-44172.35554420356</v>
       </c>
       <c r="L54" t="n">
-        <v>-51186.33540822694</v>
+        <v>-50956.81991246662</v>
       </c>
       <c r="M54" t="n">
-        <v>-57529.75388043942</v>
+        <v>-56754.60135105417</v>
       </c>
       <c r="N54" t="n">
-        <v>-63804.03451378016</v>
+        <v>-63595.23691769751</v>
       </c>
       <c r="O54" t="n">
-        <v>-42246.86482649308</v>
+        <v>-41842.01971037786</v>
       </c>
       <c r="P54" t="n">
-        <v>-47681.42019326243</v>
+        <v>-47647.48520758551</v>
       </c>
       <c r="Q54" t="n">
-        <v>-54325.19877249296</v>
+        <v>-53899.54154296016</v>
       </c>
       <c r="R54" t="n">
-        <v>-61450.39893731755</v>
+        <v>-60166.77938595962</v>
       </c>
       <c r="S54" t="n">
-        <v>-39115.73573022437</v>
+        <v>-39848.92993243043</v>
       </c>
       <c r="T54" t="n">
-        <v>-44494.41957906738</v>
+        <v>-44386.27503427226</v>
       </c>
       <c r="U54" t="n">
-        <v>-50763.255043285</v>
+        <v>-50070.10440614907</v>
       </c>
       <c r="V54" t="n">
-        <v>-56434.17753740789</v>
+        <v>-56057.97634455952</v>
       </c>
       <c r="W54" t="n">
-        <v>-38942.63821439328</v>
+        <v>-39167.95992226763</v>
       </c>
       <c r="X54" t="n">
-        <v>-44644.37657020879</v>
+        <v>-44404.79068753791</v>
       </c>
       <c r="Y54" t="n">
-        <v>-50982.48928611489</v>
+        <v>-50812.92278640328</v>
       </c>
       <c r="Z54" t="n">
-        <v>-55982.98313780118</v>
+        <v>-57673.27051660746</v>
       </c>
     </row>
     <row r="55">
@@ -5192,25 +5192,25 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.008570414741250927</v>
+        <v>0.008570414741250929</v>
       </c>
       <c r="D55" t="n">
         <v>0.008570414741250927</v>
       </c>
       <c r="E55" t="n">
-        <v>0.008570414741250929</v>
+        <v>0.008570414741250927</v>
       </c>
       <c r="F55" t="n">
         <v>0.008570414741250929</v>
       </c>
       <c r="G55" t="n">
+        <v>0.008570414741250927</v>
+      </c>
+      <c r="H55" t="n">
         <v>0.008570414741250929</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>0.008570414741250927</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.008570414741250929</v>
       </c>
       <c r="J55" t="n">
         <v>0.008570414741250929</v>
@@ -5240,25 +5240,25 @@
         <v>0.01028449768950111</v>
       </c>
       <c r="S55" t="n">
+        <v>0.008570414741250929</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.008570414741250929</v>
+      </c>
+      <c r="U55" t="n">
         <v>0.008570414741250927</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0.008570414741250927</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0.008570414741250929</v>
       </c>
       <c r="V55" t="n">
         <v>0.008570414741250927</v>
       </c>
       <c r="W55" t="n">
-        <v>0.008570414741250929</v>
+        <v>0.008570414741250927</v>
       </c>
       <c r="X55" t="n">
         <v>0.008570414741250929</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.008570414741250927</v>
+        <v>0.008570414741250929</v>
       </c>
       <c r="Z55" t="n">
         <v>0.008570414741250929</v>
@@ -5438,76 +5438,76 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.01223996382853585</v>
+        <v>0.01137018576145295</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01204603682158861</v>
+        <v>0.0115020727008736</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01219066641216545</v>
+        <v>0.01064938762623275</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01228026513321185</v>
+        <v>0.01199523955746147</v>
       </c>
       <c r="G58" t="n">
-        <v>0.01613269842251903</v>
+        <v>0.01573019163759415</v>
       </c>
       <c r="H58" t="n">
-        <v>0.01617847234674905</v>
+        <v>0.01679815026752996</v>
       </c>
       <c r="I58" t="n">
-        <v>0.01738905841286673</v>
+        <v>0.01729289069634354</v>
       </c>
       <c r="J58" t="n">
-        <v>0.01789020827045788</v>
+        <v>0.01767505552936475</v>
       </c>
       <c r="K58" t="n">
-        <v>0.01171565267106092</v>
+        <v>0.01313092906107881</v>
       </c>
       <c r="L58" t="n">
-        <v>0.01248093222326142</v>
+        <v>0.01268861084831479</v>
       </c>
       <c r="M58" t="n">
-        <v>0.01274292174594612</v>
+        <v>0.01338356908045488</v>
       </c>
       <c r="N58" t="n">
-        <v>0.01316940909075715</v>
+        <v>0.01332615601060182</v>
       </c>
       <c r="O58" t="n">
-        <v>0.01552033878740932</v>
+        <v>0.01610221066762839</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01629149984668486</v>
+        <v>0.01629165975126609</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.01571231732732477</v>
+        <v>0.01617650817485639</v>
       </c>
       <c r="R58" t="n">
-        <v>0.01509411764402605</v>
+        <v>0.01629166651261891</v>
       </c>
       <c r="S58" t="n">
-        <v>0.01915977558661076</v>
+        <v>0.01781203822137741</v>
       </c>
       <c r="T58" t="n">
-        <v>0.01936147755088544</v>
+        <v>0.01954999990147588</v>
       </c>
       <c r="U58" t="n">
-        <v>0.01852571150060645</v>
+        <v>0.0195173166344055</v>
       </c>
       <c r="V58" t="n">
-        <v>0.01887604429581725</v>
+        <v>0.01935097673551097</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01954999892606557</v>
+        <v>0.01905519852300267</v>
       </c>
       <c r="X58" t="n">
-        <v>0.01911152111568961</v>
+        <v>0.01954977366438849</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.01822652842395005</v>
+        <v>0.01845734318279209</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.01944819639282967</v>
+        <v>0.01740977058467095</v>
       </c>
     </row>
     <row r="59">
@@ -5520,76 +5520,76 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.001097282290036122</v>
+        <v>0.001076052679373169</v>
       </c>
       <c r="D59" t="n">
-        <v>0.000957207408063147</v>
+        <v>0.0009454362681808458</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0008509851577461562</v>
+        <v>0.0008199435696837409</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0007627182418088856</v>
+        <v>0.000757775893248633</v>
       </c>
       <c r="G59" t="n">
-        <v>0.001178999179999625</v>
+        <v>0.001171308787150578</v>
       </c>
       <c r="H59" t="n">
-        <v>0.001035184154302244</v>
+        <v>0.001045371589956715</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0009361397264990901</v>
+        <v>0.00093473555926621</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0008449632882065439</v>
+        <v>0.0008422363987374911</v>
       </c>
       <c r="K59" t="n">
-        <v>0.001057542409559787</v>
+        <v>0.001089588013293952</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0009421182768374834</v>
+        <v>0.0009463093109721214</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0008393745674270297</v>
+        <v>0.0008507115094758361</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0007576489152216633</v>
+        <v>0.0007601117859096615</v>
       </c>
       <c r="O59" t="n">
-        <v>0.001138510842057114</v>
+        <v>0.001149361431678749</v>
       </c>
       <c r="P59" t="n">
-        <v>0.00101045777058186</v>
+        <v>0.001011167936410945</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.0008883142112251711</v>
+        <v>0.000895247517620854</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0007863702723022081</v>
+        <v>0.0008029712649786739</v>
       </c>
       <c r="S59" t="n">
-        <v>0.001231474172868721</v>
+        <v>0.001209113642775949</v>
       </c>
       <c r="T59" t="n">
-        <v>0.001084362701215913</v>
+        <v>0.001086973472193696</v>
       </c>
       <c r="U59" t="n">
-        <v>0.0009518384578477634</v>
+        <v>0.0009648771350324031</v>
       </c>
       <c r="V59" t="n">
-        <v>0.0008570817721509907</v>
+        <v>0.0008627796477421247</v>
       </c>
       <c r="W59" t="n">
-        <v>0.00123687440450997</v>
+        <v>0.001229854149452593</v>
       </c>
       <c r="X59" t="n">
-        <v>0.001080763198712068</v>
+        <v>0.001086525585061522</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.0009477875414919836</v>
+        <v>0.0009509176876731397</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.0008639245496400728</v>
+        <v>0.0008388355225296812</v>
       </c>
     </row>
     <row r="60">
@@ -5602,76 +5602,76 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>324204.8647261992</v>
+        <v>331164.9183743042</v>
       </c>
       <c r="D60" t="n">
-        <v>372156.2317196258</v>
+        <v>377169.3560283291</v>
       </c>
       <c r="E60" t="n">
-        <v>418886.0989945632</v>
+        <v>435934.838362961</v>
       </c>
       <c r="F60" t="n">
-        <v>467689.9475716453</v>
+        <v>470962.5612329348</v>
       </c>
       <c r="G60" t="n">
-        <v>299569.9592346919</v>
+        <v>301752.8929672644</v>
       </c>
       <c r="H60" t="n">
-        <v>341641.7519204156</v>
+        <v>337964.1573744082</v>
       </c>
       <c r="I60" t="n">
-        <v>377555.0015748969</v>
+        <v>378178.7457925881</v>
       </c>
       <c r="J60" t="n">
-        <v>418512.835079296</v>
+        <v>420000.229518141</v>
       </c>
       <c r="K60" t="n">
-        <v>307448.1971369734</v>
+        <v>297602.33229556</v>
       </c>
       <c r="L60" t="n">
-        <v>344966.5569753755</v>
+        <v>343310.8268334464</v>
       </c>
       <c r="M60" t="n">
-        <v>387389.6643152762</v>
+        <v>381815.4190700296</v>
       </c>
       <c r="N60" t="n">
-        <v>429266.0538292392</v>
+        <v>427768.4145175375</v>
       </c>
       <c r="O60" t="n">
-        <v>283575.8135606217</v>
+        <v>280610.6097833536</v>
       </c>
       <c r="P60" t="n">
-        <v>319536.2491576513</v>
+        <v>319309.326582793</v>
       </c>
       <c r="Q60" t="n">
-        <v>364271.6192380075</v>
+        <v>361185.9923305382</v>
       </c>
       <c r="R60" t="n">
-        <v>412347.5009951462</v>
+        <v>403092.63872283</v>
       </c>
       <c r="S60" t="n">
-        <v>285316.4992586558</v>
+        <v>291255.9464198656</v>
       </c>
       <c r="T60" t="n">
-        <v>324468.4250174348</v>
+        <v>323593.5043255325</v>
       </c>
       <c r="U60" t="n">
-        <v>370681.3709943569</v>
+        <v>365127.3495262935</v>
       </c>
       <c r="V60" t="n">
-        <v>412006.5389403222</v>
+        <v>409007.468946603</v>
       </c>
       <c r="W60" t="n">
-        <v>283888.8459055627</v>
+        <v>285742.0892010657</v>
       </c>
       <c r="X60" t="n">
-        <v>325677.4865185978</v>
+        <v>323728.7611437076</v>
       </c>
       <c r="Y60" t="n">
-        <v>372435.1747679247</v>
+        <v>371078.8146201847</v>
       </c>
       <c r="Z60" t="n">
-        <v>408408.9253688431</v>
+        <v>421867.7216830437</v>
       </c>
     </row>
     <row r="61">
@@ -5684,76 +5684,76 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>334217.4420875125</v>
+        <v>340804.7437541328</v>
       </c>
       <c r="D61" t="n">
-        <v>383071.4170051882</v>
+        <v>387835.4699019374</v>
       </c>
       <c r="E61" t="n">
-        <v>430827.592145575</v>
+        <v>447116.7706125263</v>
       </c>
       <c r="F61" t="n">
-        <v>480616.2850706382</v>
+        <v>483746.5457848253</v>
       </c>
       <c r="G61" t="n">
-        <v>311073.6288106134</v>
+        <v>313114.1693286388</v>
       </c>
       <c r="H61" t="n">
-        <v>354245.6934469616</v>
+        <v>350796.9880674263</v>
       </c>
       <c r="I61" t="n">
-        <v>391682.5743501486</v>
+        <v>392270.2927467378</v>
       </c>
       <c r="J61" t="n">
-        <v>433894.1376625388</v>
+        <v>435297.1708447575</v>
       </c>
       <c r="K61" t="n">
-        <v>316550.6615149021</v>
+        <v>307249.7684449033</v>
       </c>
       <c r="L61" t="n">
-        <v>355289.2023514666</v>
+        <v>353717.4608905514</v>
       </c>
       <c r="M61" t="n">
-        <v>398723.2400190044</v>
+        <v>393416.3355608545</v>
       </c>
       <c r="N61" t="n">
-        <v>441672.0643046291</v>
+        <v>440242.9880855926</v>
       </c>
       <c r="O61" t="n">
-        <v>294059.3224370614</v>
+        <v>291285.8169263371</v>
       </c>
       <c r="P61" t="n">
-        <v>331285.5327355003</v>
+        <v>331053.1085508364</v>
       </c>
       <c r="Q61" t="n">
-        <v>376782.8241796896</v>
+        <v>373868.2742015133</v>
       </c>
       <c r="R61" t="n">
-        <v>425562.2909888969</v>
+        <v>416775.6885312758</v>
       </c>
       <c r="S61" t="n">
-        <v>297829.7720936845</v>
+        <v>303332.7824963627</v>
       </c>
       <c r="T61" t="n">
-        <v>338195.5491904656</v>
+        <v>337384.0427281096</v>
       </c>
       <c r="U61" t="n">
-        <v>385229.7563705973</v>
+        <v>380029.7752765026</v>
       </c>
       <c r="V61" t="n">
-        <v>427766.8262064709</v>
+        <v>424945.3013776663</v>
       </c>
       <c r="W61" t="n">
-        <v>296530.5579680347</v>
+        <v>298221.7481087364</v>
       </c>
       <c r="X61" t="n">
-        <v>339320.80597042</v>
+        <v>337522.9827151944</v>
       </c>
       <c r="Y61" t="n">
-        <v>386874.4078659168</v>
+        <v>385602.3552358158</v>
       </c>
       <c r="Z61" t="n">
-        <v>424382.843626494</v>
+        <v>437059.7485018063</v>
       </c>
     </row>
     <row r="62">
@@ -5848,76 +5848,76 @@
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>8234.845185824512</v>
+        <v>8385.474233894345</v>
       </c>
       <c r="D63" t="n">
-        <v>9352.105697264007</v>
+        <v>9461.073656178265</v>
       </c>
       <c r="E63" t="n">
-        <v>10444.56700955972</v>
+        <v>10817.26460127504</v>
       </c>
       <c r="F63" t="n">
-        <v>11583.84691797099</v>
+        <v>11655.48551255381</v>
       </c>
       <c r="G63" t="n">
-        <v>7705.671107909882</v>
+        <v>7752.324392573518</v>
       </c>
       <c r="H63" t="n">
-        <v>8692.840655216185</v>
+        <v>8613.973681760061</v>
       </c>
       <c r="I63" t="n">
-        <v>9549.070499232708</v>
+        <v>9562.513864508786</v>
       </c>
       <c r="J63" t="n">
-        <v>10514.72709702502</v>
+        <v>10546.82778152398</v>
       </c>
       <c r="K63" t="n">
-        <v>8521.744162543831</v>
+        <v>8288.759703079313</v>
       </c>
       <c r="L63" t="n">
-        <v>9492.280954037711</v>
+        <v>9452.898637303579</v>
       </c>
       <c r="M63" t="n">
-        <v>10580.74129795585</v>
+        <v>10447.73371026167</v>
       </c>
       <c r="N63" t="n">
-        <v>11657.33835456199</v>
+        <v>11621.51099992081</v>
       </c>
       <c r="O63" t="n">
-        <v>7958.366824540537</v>
+        <v>7888.899887076035</v>
       </c>
       <c r="P63" t="n">
-        <v>8890.876327022212</v>
+        <v>8885.053459377177</v>
       </c>
       <c r="Q63" t="n">
-        <v>10030.87513822203</v>
+        <v>9957.83707263042</v>
       </c>
       <c r="R63" t="n">
-        <v>11253.48056081298</v>
+        <v>11033.22566442684</v>
       </c>
       <c r="S63" t="n">
-        <v>7402.88762374707</v>
+        <v>7528.695627268814</v>
       </c>
       <c r="T63" t="n">
-        <v>8325.810192640221</v>
+        <v>8307.253786668236</v>
       </c>
       <c r="U63" t="n">
-        <v>9401.472918540856</v>
+        <v>9282.535947223416</v>
       </c>
       <c r="V63" t="n">
-        <v>10374.54040184268</v>
+        <v>10309.98844432263</v>
       </c>
       <c r="W63" t="n">
-        <v>7373.186007428012</v>
+        <v>7411.848716615413</v>
       </c>
       <c r="X63" t="n">
-        <v>8351.541151249638</v>
+        <v>8310.430867671117</v>
       </c>
       <c r="Y63" t="n">
-        <v>9439.09108615735</v>
+        <v>9409.995353091403</v>
       </c>
       <c r="Z63" t="n">
-        <v>10297.12044074108</v>
+        <v>10587.15503166635</v>
       </c>
     </row>
     <row r="64">
@@ -5930,76 +5930,76 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0004524024335587134</v>
+        <v>0.0004592357918504256</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0005082373281138363</v>
+        <v>0.0005132289652275312</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0005631174277598759</v>
+        <v>0.0005803711751955497</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0006202974359039807</v>
+        <v>0.0006236237148602662</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0004287334392055473</v>
+        <v>0.0004307986735049571</v>
       </c>
       <c r="H64" t="n">
-        <v>0.000478370142789825</v>
+        <v>0.0004748458517427791</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0005222857737500693</v>
+        <v>0.0005228925761492984</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0005712178048896484</v>
+        <v>0.0005726731346735095</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0004181070110481928</v>
+        <v>0.0004086568677668358</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0004622902144656813</v>
+        <v>0.0004606757154485649</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0005114179974330438</v>
+        <v>0.0005059298258285079</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0005601523597125956</v>
+        <v>0.0005586662876097977</v>
       </c>
       <c r="O64" t="n">
-        <v>0.0003953795027363424</v>
+        <v>0.0003926163070019001</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0004378795919473506</v>
+        <v>0.0004376173174613596</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0004888505820205399</v>
+        <v>0.000485877989168187</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0005434601215880187</v>
+        <v>0.0005344046847241241</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0004154876318821159</v>
+        <v>0.0004209590537309185</v>
       </c>
       <c r="T64" t="n">
-        <v>0.0004620764341138331</v>
+        <v>0.0004612639515308493</v>
       </c>
       <c r="U64" t="n">
-        <v>0.000515662965635828</v>
+        <v>0.000510353187111553</v>
       </c>
       <c r="V64" t="n">
-        <v>0.0005648801928837792</v>
+        <v>0.0005619680542269398</v>
       </c>
       <c r="W64" t="n">
-        <v>0.0004142347479661485</v>
+        <v>0.0004158732756689494</v>
       </c>
       <c r="X64" t="n">
-        <v>0.000463209263294825</v>
+        <v>0.0004614237875321017</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.0005173474968421912</v>
+        <v>0.0005160443878606222</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.0005613886478536237</v>
+        <v>0.0005745032874295604</v>
       </c>
     </row>
     <row r="65">
@@ -6012,76 +6012,76 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1249059757969552</v>
+        <v>0.1243646936710681</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1276765253005694</v>
+        <v>0.1273178677640922</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1305970073342885</v>
+        <v>0.1295241527870215</v>
       </c>
       <c r="F65" t="n">
-        <v>0.133433894253751</v>
+        <v>0.1332320009697328</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1271377677004273</v>
+        <v>0.1269211244767985</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1301748105170184</v>
+        <v>0.1305225132470466</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1338259271815787</v>
+        <v>0.1337716972302615</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1370416041514705</v>
+        <v>0.1369140296660327</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1241131737501908</v>
+        <v>0.1250009771774967</v>
       </c>
       <c r="L65" t="n">
-        <v>0.1274840106491392</v>
+        <v>0.1276193040710628</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1304899412777374</v>
+        <v>0.1309188130552169</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1335672572034989</v>
+        <v>0.1336770724200655</v>
       </c>
       <c r="O65" t="n">
-        <v>0.1263851202925502</v>
+        <v>0.1267079947306347</v>
       </c>
       <c r="P65" t="n">
-        <v>0.129837057472915</v>
+        <v>0.1298205187233279</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1324064724147185</v>
+        <v>0.1326901034341674</v>
       </c>
       <c r="R65" t="n">
-        <v>0.1348759669657416</v>
+        <v>0.135642941582089</v>
       </c>
       <c r="S65" t="n">
-        <v>0.128700726665305</v>
+        <v>0.1280202119946605</v>
       </c>
       <c r="T65" t="n">
-        <v>0.1318987911549706</v>
+        <v>0.1319981433518655</v>
       </c>
       <c r="U65" t="n">
-        <v>0.1344678609370295</v>
+        <v>0.1350123650250046</v>
       </c>
       <c r="V65" t="n">
-        <v>0.1376179810348939</v>
+        <v>0.1378888148802876</v>
       </c>
       <c r="W65" t="n">
-        <v>0.1289085560138306</v>
+        <v>0.1286475727068713</v>
       </c>
       <c r="X65" t="n">
-        <v>0.131768676498106</v>
+        <v>0.1320081529997294</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.1343007922506581</v>
+        <v>0.1344297996802971</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.1379440752940333</v>
+        <v>0.1367556951948004</v>
       </c>
     </row>
     <row r="66">
@@ -6094,76 +6094,76 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.004865827404278021</v>
+        <v>0.004694214100875902</v>
       </c>
       <c r="D66" t="n">
-        <v>0.005448413098725112</v>
+        <v>0.005326147241458934</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0061285918589937</v>
+        <v>0.005739165364558636</v>
       </c>
       <c r="F66" t="n">
-        <v>0.006825772192514711</v>
+        <v>0.006746503616428662</v>
       </c>
       <c r="G66" t="n">
-        <v>0.005608199853186453</v>
+        <v>0.005533562408675076</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00634251287627954</v>
+        <v>0.006472412476343871</v>
       </c>
       <c r="I66" t="n">
-        <v>0.007379548706685709</v>
+        <v>0.007357449044433379</v>
       </c>
       <c r="J66" t="n">
-        <v>0.008320778140428047</v>
+        <v>0.008265447778721458</v>
       </c>
       <c r="K66" t="n">
-        <v>0.004776800039027676</v>
+        <v>0.005063915367030269</v>
       </c>
       <c r="L66" t="n">
-        <v>0.00556991814882161</v>
+        <v>0.005617355048354295</v>
       </c>
       <c r="M66" t="n">
-        <v>0.006300506691745793</v>
+        <v>0.006463230549543808</v>
       </c>
       <c r="N66" t="n">
-        <v>0.00711631897185542</v>
+        <v>0.007160712671888096</v>
       </c>
       <c r="O66" t="n">
-        <v>0.005531029041434421</v>
+        <v>0.005642824285569512</v>
       </c>
       <c r="P66" t="n">
-        <v>0.006421884430475183</v>
+        <v>0.006417706558352106</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.007042996205350701</v>
+        <v>0.007156308685974692</v>
       </c>
       <c r="R66" t="n">
-        <v>0.007654220645883047</v>
+        <v>0.007979395652777478</v>
       </c>
       <c r="S66" t="n">
-        <v>0.006160517190542838</v>
+        <v>0.005916878985878629</v>
       </c>
       <c r="T66" t="n">
-        <v>0.006999492048916942</v>
+        <v>0.007038115843948891</v>
       </c>
       <c r="U66" t="n">
-        <v>0.007641993827948534</v>
+        <v>0.007868112799243598</v>
       </c>
       <c r="V66" t="n">
-        <v>0.008572814686584872</v>
+        <v>0.008692725713926767</v>
       </c>
       <c r="W66" t="n">
-        <v>0.006234211197598393</v>
+        <v>0.006141443450452091</v>
       </c>
       <c r="X66" t="n">
-        <v>0.006948784928663795</v>
+        <v>0.00704078701709902</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.007573258632826776</v>
+        <v>0.007626308023931075</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.008717257442625484</v>
+        <v>0.008197024545348264</v>
       </c>
     </row>
     <row r="67">
@@ -6258,76 +6258,76 @@
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>27.77334229769439</v>
+        <v>26.79380179569577</v>
       </c>
       <c r="D68" t="n">
-        <v>31.09864559459994</v>
+        <v>30.40077219650344</v>
       </c>
       <c r="E68" t="n">
-        <v>34.9809940552034</v>
+        <v>32.75821169341491</v>
       </c>
       <c r="F68" t="n">
-        <v>38.96038469883286</v>
+        <v>38.50793270779982</v>
       </c>
       <c r="G68" t="n">
-        <v>21.19977633079235</v>
+        <v>20.91763639802157</v>
       </c>
       <c r="H68" t="n">
-        <v>23.97558180382955</v>
+        <v>24.46662037929304</v>
       </c>
       <c r="I68" t="n">
-        <v>27.89572163963389</v>
+        <v>27.81218183916312</v>
       </c>
       <c r="J68" t="n">
-        <v>31.45369995596629</v>
+        <v>31.24454348451582</v>
       </c>
       <c r="K68" t="n">
-        <v>27.26518874362755</v>
+        <v>28.90399579965259</v>
       </c>
       <c r="L68" t="n">
-        <v>31.79217643053991</v>
+        <v>32.06293844875377</v>
       </c>
       <c r="M68" t="n">
-        <v>35.96225563712407</v>
+        <v>36.89105664610604</v>
       </c>
       <c r="N68" t="n">
-        <v>40.61877791455348</v>
+        <v>40.87216985068847</v>
       </c>
       <c r="O68" t="n">
-        <v>20.90805991710584</v>
+        <v>21.33066150630628</v>
       </c>
       <c r="P68" t="n">
-        <v>24.27561733038429</v>
+        <v>24.25982439203214</v>
       </c>
       <c r="Q68" t="n">
-        <v>26.62350632301728</v>
+        <v>27.05184327740577</v>
       </c>
       <c r="R68" t="n">
-        <v>28.93401981512065</v>
+        <v>30.16322661854955</v>
       </c>
       <c r="S68" t="n">
-        <v>35.16321859533033</v>
+        <v>33.77257180646446</v>
       </c>
       <c r="T68" t="n">
-        <v>39.95194905878602</v>
+        <v>40.17240732644163</v>
       </c>
       <c r="U68" t="n">
-        <v>43.61924350910566</v>
+        <v>44.90989339616473</v>
       </c>
       <c r="V68" t="n">
-        <v>48.93221583155422</v>
+        <v>49.61664824785953</v>
       </c>
       <c r="W68" t="n">
-        <v>23.56618637848908</v>
+        <v>23.21551137729494</v>
       </c>
       <c r="X68" t="n">
-        <v>26.26737457916261</v>
+        <v>26.61515528381855</v>
       </c>
       <c r="Y68" t="n">
-        <v>28.62797213261724</v>
+        <v>28.82850621758871</v>
       </c>
       <c r="Z68" t="n">
-        <v>32.95244692405063</v>
+        <v>30.98589413511413</v>
       </c>
     </row>
     <row r="69">
@@ -6340,76 +6340,76 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>49.88984076553704</v>
+        <v>50.84858755150581</v>
       </c>
       <c r="D69" t="n">
-        <v>56.67237916392974</v>
+        <v>57.36562152211854</v>
       </c>
       <c r="E69" t="n">
-        <v>63.28478574024041</v>
+        <v>65.65075272966982</v>
       </c>
       <c r="F69" t="n">
-        <v>70.18272658578665</v>
+        <v>70.63828645934537</v>
       </c>
       <c r="G69" t="n">
-        <v>46.49695869164092</v>
+        <v>46.79771151785435</v>
       </c>
       <c r="H69" t="n">
-        <v>52.45085172544546</v>
+        <v>51.94177153689651</v>
       </c>
       <c r="I69" t="n">
-        <v>57.5441138774191</v>
+        <v>57.63088222019478</v>
       </c>
       <c r="J69" t="n">
-        <v>63.32875766355882</v>
+        <v>63.53640065674242</v>
       </c>
       <c r="K69" t="n">
-        <v>55.71407679120131</v>
+        <v>54.11105311867651</v>
       </c>
       <c r="L69" t="n">
-        <v>62.01173560340437</v>
+        <v>61.74097921537607</v>
       </c>
       <c r="M69" t="n">
-        <v>69.10493751555619</v>
+        <v>68.19002022675612</v>
       </c>
       <c r="N69" t="n">
-        <v>76.10302699371765</v>
+        <v>75.85647456734331</v>
       </c>
       <c r="O69" t="n">
-        <v>51.82636704564776</v>
+        <v>51.34340437076644</v>
       </c>
       <c r="P69" t="n">
-        <v>57.85266405951202</v>
+        <v>57.81476948847833</v>
       </c>
       <c r="Q69" t="n">
-        <v>65.30925175161956</v>
+        <v>64.80226921637505</v>
       </c>
       <c r="R69" t="n">
-        <v>73.31664597421663</v>
+        <v>71.79093871915445</v>
       </c>
       <c r="S69" t="n">
-        <v>83.62242293349706</v>
+        <v>85.15943661283295</v>
       </c>
       <c r="T69" t="n">
-        <v>94.0240792018552</v>
+        <v>93.79647879498715</v>
       </c>
       <c r="U69" t="n">
-        <v>106.2587368892422</v>
+        <v>104.8070692556884</v>
       </c>
       <c r="V69" t="n">
-        <v>117.2101514055538</v>
+        <v>116.4232079543707</v>
       </c>
       <c r="W69" t="n">
-        <v>83.25417274552035</v>
+        <v>83.73247404569933</v>
       </c>
       <c r="X69" t="n">
-        <v>94.33872961128665</v>
+        <v>93.83235777062916</v>
       </c>
       <c r="Y69" t="n">
-        <v>106.7169538560849</v>
+        <v>106.3625842691499</v>
       </c>
       <c r="Z69" t="n">
-        <v>116.2661269748129</v>
+        <v>119.7957301377892</v>
       </c>
     </row>
     <row r="70">
@@ -6422,76 +6422,76 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>101261407.9709393</v>
+        <v>106920389.3174575</v>
       </c>
       <c r="D70" t="n">
-        <v>148322099.6348288</v>
+        <v>153567359.0596501</v>
       </c>
       <c r="E70" t="n">
-        <v>206608872.0053105</v>
+        <v>229525004.3756305</v>
       </c>
       <c r="F70" t="n">
-        <v>281861704.4824673</v>
+        <v>287123508.1348287</v>
       </c>
       <c r="G70" t="n">
-        <v>82967699.97114399</v>
+        <v>84483803.31676599</v>
       </c>
       <c r="H70" t="n">
-        <v>119113997.9200473</v>
+        <v>115901289.1491397</v>
       </c>
       <c r="I70" t="n">
-        <v>157892297.4219048</v>
+        <v>158560088.1163581</v>
       </c>
       <c r="J70" t="n">
-        <v>210800511.8111266</v>
+        <v>212737087.1535474</v>
       </c>
       <c r="K70" t="n">
-        <v>105617086.1451304</v>
+        <v>97189053.84750059</v>
       </c>
       <c r="L70" t="n">
-        <v>145968941.393987</v>
+        <v>144159646.7024636</v>
       </c>
       <c r="M70" t="n">
-        <v>202160821.6090918</v>
+        <v>194632334.0780679</v>
       </c>
       <c r="N70" t="n">
-        <v>270362785.6186702</v>
+        <v>267877661.5536912</v>
       </c>
       <c r="O70" t="n">
-        <v>86024184.80798472</v>
+        <v>83791128.68283521</v>
       </c>
       <c r="P70" t="n">
-        <v>119945073.2162441</v>
+        <v>119709562.0212225</v>
       </c>
       <c r="Q70" t="n">
-        <v>172252359.530477</v>
+        <v>168517013.880985</v>
       </c>
       <c r="R70" t="n">
-        <v>243225610.1262656</v>
+        <v>229221953.3728202</v>
       </c>
       <c r="S70" t="n">
-        <v>73566672.93233466</v>
+        <v>77381450.1103884</v>
       </c>
       <c r="T70" t="n">
-        <v>104654320.5664273</v>
+        <v>103956124.3838412</v>
       </c>
       <c r="U70" t="n">
-        <v>150683376.4405668</v>
+        <v>145036584.5924262</v>
       </c>
       <c r="V70" t="n">
-        <v>202480984.5660015</v>
+        <v>198724851.2274658</v>
       </c>
       <c r="W70" t="n">
-        <v>72684735.71479771</v>
+        <v>73834150.76337947</v>
       </c>
       <c r="X70" t="n">
-        <v>105627626.5102592</v>
+        <v>104075443.0055525</v>
       </c>
       <c r="Y70" t="n">
-        <v>152499414.3989496</v>
+        <v>151093531.4324168</v>
       </c>
       <c r="Z70" t="n">
-        <v>197981687.9016345</v>
+        <v>215186718.5766517</v>
       </c>
     </row>
     <row r="71">
@@ -6504,76 +6504,76 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>77.66318306323143</v>
+        <v>77.64238934720159</v>
       </c>
       <c r="D71" t="n">
-        <v>87.77102475852968</v>
+        <v>87.76639371862197</v>
       </c>
       <c r="E71" t="n">
-        <v>98.26577979544381</v>
+        <v>98.40896442308474</v>
       </c>
       <c r="F71" t="n">
-        <v>109.1431112846195</v>
+        <v>109.1462191671452</v>
       </c>
       <c r="G71" t="n">
-        <v>67.69673502243327</v>
+        <v>67.71534791587592</v>
       </c>
       <c r="H71" t="n">
-        <v>76.42643352927502</v>
+        <v>76.40839191618954</v>
       </c>
       <c r="I71" t="n">
-        <v>85.439835517053</v>
+        <v>85.44306405935789</v>
       </c>
       <c r="J71" t="n">
-        <v>94.7824576195251</v>
+        <v>94.78094414125823</v>
       </c>
       <c r="K71" t="n">
-        <v>82.97926553482887</v>
+        <v>83.0150489183291</v>
       </c>
       <c r="L71" t="n">
-        <v>93.80391203394427</v>
+        <v>93.80391766412984</v>
       </c>
       <c r="M71" t="n">
-        <v>105.0671931526803</v>
+        <v>105.0810768728622</v>
       </c>
       <c r="N71" t="n">
-        <v>116.7218049082711</v>
+        <v>116.7286444180318</v>
       </c>
       <c r="O71" t="n">
-        <v>72.7344269627536</v>
+        <v>72.67406587707271</v>
       </c>
       <c r="P71" t="n">
-        <v>82.12828138989632</v>
+        <v>82.07459388051048</v>
       </c>
       <c r="Q71" t="n">
-        <v>91.93275807463684</v>
+        <v>91.85411249378082</v>
       </c>
       <c r="R71" t="n">
-        <v>102.2506657893373</v>
+        <v>101.954165337704</v>
       </c>
       <c r="S71" t="n">
-        <v>118.7856415288274</v>
+        <v>118.9320084192974</v>
       </c>
       <c r="T71" t="n">
-        <v>133.9760282606412</v>
+        <v>133.9688861214288</v>
       </c>
       <c r="U71" t="n">
-        <v>149.8779803983479</v>
+        <v>149.7169626518532</v>
       </c>
       <c r="V71" t="n">
-        <v>166.142367237108</v>
+        <v>166.0398562022302</v>
       </c>
       <c r="W71" t="n">
-        <v>106.8203591240094</v>
+        <v>106.9479854229943</v>
       </c>
       <c r="X71" t="n">
-        <v>120.6061041904493</v>
+        <v>120.4475130544477</v>
       </c>
       <c r="Y71" t="n">
-        <v>135.3449259887022</v>
+        <v>135.1910904867386</v>
       </c>
       <c r="Z71" t="n">
-        <v>149.2185738988636</v>
+        <v>150.7816242729033</v>
       </c>
     </row>
     <row r="72">
@@ -6668,76 +6668,76 @@
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>101261407.9709393</v>
+        <v>106920389.3174575</v>
       </c>
       <c r="D73" t="n">
-        <v>148322099.6348288</v>
+        <v>153567359.0596501</v>
       </c>
       <c r="E73" t="n">
-        <v>206608872.0053105</v>
+        <v>229525004.3756305</v>
       </c>
       <c r="F73" t="n">
-        <v>281861704.4824673</v>
+        <v>287123508.1348287</v>
       </c>
       <c r="G73" t="n">
-        <v>82967699.97114399</v>
+        <v>84483803.31676599</v>
       </c>
       <c r="H73" t="n">
-        <v>119113997.9200473</v>
+        <v>115901289.1491397</v>
       </c>
       <c r="I73" t="n">
-        <v>157892297.4219048</v>
+        <v>158560088.1163581</v>
       </c>
       <c r="J73" t="n">
-        <v>210800511.8111266</v>
+        <v>212737087.1535474</v>
       </c>
       <c r="K73" t="n">
-        <v>105617086.1451304</v>
+        <v>97189053.84750059</v>
       </c>
       <c r="L73" t="n">
-        <v>145968941.393987</v>
+        <v>144159646.7024636</v>
       </c>
       <c r="M73" t="n">
-        <v>202160821.6090918</v>
+        <v>194632334.0780679</v>
       </c>
       <c r="N73" t="n">
-        <v>270362785.6186702</v>
+        <v>267877661.5536912</v>
       </c>
       <c r="O73" t="n">
-        <v>86024184.80798472</v>
+        <v>83791128.68283521</v>
       </c>
       <c r="P73" t="n">
-        <v>119945073.2162441</v>
+        <v>119709562.0212225</v>
       </c>
       <c r="Q73" t="n">
-        <v>172252359.530477</v>
+        <v>168517013.880985</v>
       </c>
       <c r="R73" t="n">
-        <v>243225610.1262656</v>
+        <v>229221953.3728202</v>
       </c>
       <c r="S73" t="n">
-        <v>73566672.93233466</v>
+        <v>77381450.1103884</v>
       </c>
       <c r="T73" t="n">
-        <v>104654320.5664273</v>
+        <v>103956124.3838412</v>
       </c>
       <c r="U73" t="n">
-        <v>150683376.4405668</v>
+        <v>145036584.5924262</v>
       </c>
       <c r="V73" t="n">
-        <v>202480984.5660015</v>
+        <v>198724851.2274658</v>
       </c>
       <c r="W73" t="n">
-        <v>72684735.71479771</v>
+        <v>73834150.76337947</v>
       </c>
       <c r="X73" t="n">
-        <v>105627626.5102592</v>
+        <v>104075443.0055525</v>
       </c>
       <c r="Y73" t="n">
-        <v>152499414.3989496</v>
+        <v>151093531.4324168</v>
       </c>
       <c r="Z73" t="n">
-        <v>197981687.9016345</v>
+        <v>215186718.5766517</v>
       </c>
     </row>
     <row r="74">
@@ -6832,76 +6832,76 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>46050411.69656394</v>
+        <v>46594748.42442953</v>
       </c>
       <c r="D75" t="n">
-        <v>68712394.43046138</v>
+        <v>69236563.73452319</v>
       </c>
       <c r="E75" t="n">
-        <v>98630836.47048153</v>
+        <v>101085303.444483</v>
       </c>
       <c r="F75" t="n">
-        <v>137794166.9918855</v>
+        <v>138403004.2633289</v>
       </c>
       <c r="G75" t="n">
-        <v>44141953.92056517</v>
+        <v>44316949.58845565</v>
       </c>
       <c r="H75" t="n">
-        <v>65435410.40435749</v>
+        <v>65045183.80165782</v>
       </c>
       <c r="I75" t="n">
-        <v>92733387.01562506</v>
+        <v>92830522.55062731</v>
       </c>
       <c r="J75" t="n">
-        <v>128649516.706825</v>
+        <v>128923982.8076504</v>
       </c>
       <c r="K75" t="n">
-        <v>47088956.06094465</v>
+        <v>46283488.06914904</v>
       </c>
       <c r="L75" t="n">
-        <v>69391012.06961772</v>
+        <v>69196146.44416575</v>
       </c>
       <c r="M75" t="n">
-        <v>99540348.96497533</v>
+        <v>98651692.46929404</v>
       </c>
       <c r="N75" t="n">
-        <v>138418844.1550689</v>
+        <v>138119262.7872498</v>
       </c>
       <c r="O75" t="n">
-        <v>45053143.57918839</v>
+        <v>44802574.31655795</v>
       </c>
       <c r="P75" t="n">
-        <v>66532273.10605856</v>
+        <v>66391902.27161539</v>
       </c>
       <c r="Q75" t="n">
-        <v>95906393.06605142</v>
+        <v>95425388.16768847</v>
       </c>
       <c r="R75" t="n">
-        <v>135038577.1456264</v>
+        <v>133107005.5727926</v>
       </c>
       <c r="S75" t="n">
-        <v>43055524.74886276</v>
+        <v>43503307.98606241</v>
       </c>
       <c r="T75" t="n">
-        <v>63619373.6173722</v>
+        <v>63538521.17483882</v>
       </c>
       <c r="U75" t="n">
-        <v>91761361.05592145</v>
+        <v>90978073.14505449</v>
       </c>
       <c r="V75" t="n">
-        <v>127462810.074442</v>
+        <v>126899002.0829406</v>
       </c>
       <c r="W75" t="n">
-        <v>43019496.66405376</v>
+        <v>43081835.76439343</v>
       </c>
       <c r="X75" t="n">
-        <v>63746688.9723024</v>
+        <v>63617205.84935191</v>
       </c>
       <c r="Y75" t="n">
-        <v>92009094.62576807</v>
+        <v>91817487.11856285</v>
       </c>
       <c r="Z75" t="n">
-        <v>126788984.8123903</v>
+        <v>129268775.8225761</v>
       </c>
     </row>
     <row r="76">
@@ -13476,76 +13476,76 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>8234.845185824512</v>
+        <v>8385.474233894345</v>
       </c>
       <c r="D149" t="n">
-        <v>9352.105697264007</v>
+        <v>9461.073656178265</v>
       </c>
       <c r="E149" t="n">
-        <v>10444.56700955972</v>
+        <v>10817.26460127504</v>
       </c>
       <c r="F149" t="n">
-        <v>11583.84691797099</v>
+        <v>11655.48551255381</v>
       </c>
       <c r="G149" t="n">
-        <v>7705.671107909882</v>
+        <v>7752.324392573518</v>
       </c>
       <c r="H149" t="n">
-        <v>8692.840655216185</v>
+        <v>8613.973681760061</v>
       </c>
       <c r="I149" t="n">
-        <v>9549.070499232708</v>
+        <v>9562.513864508786</v>
       </c>
       <c r="J149" t="n">
-        <v>10514.72709702502</v>
+        <v>10546.82778152398</v>
       </c>
       <c r="K149" t="n">
-        <v>8521.744162543831</v>
+        <v>8288.759703079313</v>
       </c>
       <c r="L149" t="n">
-        <v>9492.280954037711</v>
+        <v>9452.898637303579</v>
       </c>
       <c r="M149" t="n">
-        <v>10580.74129795585</v>
+        <v>10447.73371026167</v>
       </c>
       <c r="N149" t="n">
-        <v>11657.33835456199</v>
+        <v>11621.51099992081</v>
       </c>
       <c r="O149" t="n">
-        <v>7958.366824540537</v>
+        <v>7888.899887076035</v>
       </c>
       <c r="P149" t="n">
-        <v>8890.876327022212</v>
+        <v>8885.053459377177</v>
       </c>
       <c r="Q149" t="n">
-        <v>10030.87513822203</v>
+        <v>9957.83707263042</v>
       </c>
       <c r="R149" t="n">
-        <v>11253.48056081298</v>
+        <v>11033.22566442684</v>
       </c>
       <c r="S149" t="n">
-        <v>7402.88762374707</v>
+        <v>7528.695627268814</v>
       </c>
       <c r="T149" t="n">
-        <v>8325.810192640221</v>
+        <v>8307.253786668236</v>
       </c>
       <c r="U149" t="n">
-        <v>9401.472918540856</v>
+        <v>9282.535947223416</v>
       </c>
       <c r="V149" t="n">
-        <v>10374.54040184268</v>
+        <v>10309.98844432263</v>
       </c>
       <c r="W149" t="n">
-        <v>7373.186007428012</v>
+        <v>7411.848716615413</v>
       </c>
       <c r="X149" t="n">
-        <v>8351.541151249638</v>
+        <v>8310.430867671117</v>
       </c>
       <c r="Y149" t="n">
-        <v>9439.09108615735</v>
+        <v>9409.995353091403</v>
       </c>
       <c r="Z149" t="n">
-        <v>10297.12044074108</v>
+        <v>10587.15503166635</v>
       </c>
     </row>
     <row r="150">
@@ -13722,76 +13722,76 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>12166.84518582451</v>
+        <v>12317.47423389435</v>
       </c>
       <c r="D152" t="n">
-        <v>13284.10569726401</v>
+        <v>13393.07365617827</v>
       </c>
       <c r="E152" t="n">
-        <v>14376.56700955972</v>
+        <v>14749.26460127504</v>
       </c>
       <c r="F152" t="n">
-        <v>15515.84691797099</v>
+        <v>15587.48551255381</v>
       </c>
       <c r="G152" t="n">
-        <v>11637.67110790988</v>
+        <v>11684.32439257352</v>
       </c>
       <c r="H152" t="n">
-        <v>12624.84065521619</v>
+        <v>12545.97368176006</v>
       </c>
       <c r="I152" t="n">
-        <v>13481.07049923271</v>
+        <v>13494.51386450879</v>
       </c>
       <c r="J152" t="n">
-        <v>14446.72709702502</v>
+        <v>14478.82778152398</v>
       </c>
       <c r="K152" t="n">
-        <v>12453.74416254383</v>
+        <v>12220.75970307931</v>
       </c>
       <c r="L152" t="n">
-        <v>13424.28095403771</v>
+        <v>13384.89863730358</v>
       </c>
       <c r="M152" t="n">
-        <v>14512.74129795585</v>
+        <v>14379.73371026167</v>
       </c>
       <c r="N152" t="n">
-        <v>15589.33835456199</v>
+        <v>15553.51099992081</v>
       </c>
       <c r="O152" t="n">
-        <v>11890.36682454054</v>
+        <v>11820.89988707604</v>
       </c>
       <c r="P152" t="n">
-        <v>12822.87632702221</v>
+        <v>12817.05345937718</v>
       </c>
       <c r="Q152" t="n">
-        <v>13962.87513822203</v>
+        <v>13889.83707263042</v>
       </c>
       <c r="R152" t="n">
-        <v>15185.48056081298</v>
+        <v>14965.22566442684</v>
       </c>
       <c r="S152" t="n">
-        <v>11334.88762374707</v>
+        <v>11460.69562726881</v>
       </c>
       <c r="T152" t="n">
-        <v>12257.81019264022</v>
+        <v>12239.25378666824</v>
       </c>
       <c r="U152" t="n">
-        <v>13333.47291854086</v>
+        <v>13214.53594722342</v>
       </c>
       <c r="V152" t="n">
-        <v>14306.54040184268</v>
+        <v>14241.98844432263</v>
       </c>
       <c r="W152" t="n">
-        <v>11305.18600742801</v>
+        <v>11343.84871661541</v>
       </c>
       <c r="X152" t="n">
-        <v>12283.54115124964</v>
+        <v>12242.43086767112</v>
       </c>
       <c r="Y152" t="n">
-        <v>13371.09108615735</v>
+        <v>13341.9953530914</v>
       </c>
       <c r="Z152" t="n">
-        <v>14229.12044074108</v>
+        <v>14519.15503166635</v>
       </c>
     </row>
     <row r="153">
@@ -14132,76 +14132,76 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>14166.84518582451</v>
+        <v>14317.47423389435</v>
       </c>
       <c r="D157" t="n">
-        <v>15284.10569726401</v>
+        <v>15393.07365617827</v>
       </c>
       <c r="E157" t="n">
-        <v>16376.56700955972</v>
+        <v>16749.26460127504</v>
       </c>
       <c r="F157" t="n">
-        <v>17515.84691797099</v>
+        <v>17587.48551255381</v>
       </c>
       <c r="G157" t="n">
-        <v>13637.67110790988</v>
+        <v>13684.32439257352</v>
       </c>
       <c r="H157" t="n">
-        <v>14624.84065521619</v>
+        <v>14545.97368176006</v>
       </c>
       <c r="I157" t="n">
-        <v>15481.07049923271</v>
+        <v>15494.51386450879</v>
       </c>
       <c r="J157" t="n">
-        <v>16446.72709702502</v>
+        <v>16478.82778152398</v>
       </c>
       <c r="K157" t="n">
-        <v>14453.74416254383</v>
+        <v>14220.75970307931</v>
       </c>
       <c r="L157" t="n">
-        <v>15424.28095403771</v>
+        <v>15384.89863730358</v>
       </c>
       <c r="M157" t="n">
-        <v>16512.74129795585</v>
+        <v>16379.73371026167</v>
       </c>
       <c r="N157" t="n">
-        <v>17589.33835456199</v>
+        <v>17553.51099992081</v>
       </c>
       <c r="O157" t="n">
-        <v>13890.36682454054</v>
+        <v>13820.89988707604</v>
       </c>
       <c r="P157" t="n">
-        <v>14822.87632702221</v>
+        <v>14817.05345937718</v>
       </c>
       <c r="Q157" t="n">
-        <v>15962.87513822203</v>
+        <v>15889.83707263042</v>
       </c>
       <c r="R157" t="n">
-        <v>17185.48056081298</v>
+        <v>16965.22566442683</v>
       </c>
       <c r="S157" t="n">
-        <v>13334.88762374707</v>
+        <v>13460.69562726881</v>
       </c>
       <c r="T157" t="n">
-        <v>14257.81019264022</v>
+        <v>14239.25378666824</v>
       </c>
       <c r="U157" t="n">
-        <v>15333.47291854086</v>
+        <v>15214.53594722342</v>
       </c>
       <c r="V157" t="n">
-        <v>16306.54040184268</v>
+        <v>16241.98844432263</v>
       </c>
       <c r="W157" t="n">
-        <v>13305.18600742801</v>
+        <v>13343.84871661541</v>
       </c>
       <c r="X157" t="n">
-        <v>14283.54115124964</v>
+        <v>14242.43086767112</v>
       </c>
       <c r="Y157" t="n">
-        <v>15371.09108615735</v>
+        <v>15341.9953530914</v>
       </c>
       <c r="Z157" t="n">
-        <v>16229.12044074108</v>
+        <v>16519.15503166636</v>
       </c>
     </row>
     <row r="158">
@@ -14214,76 +14214,76 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>13166.84518582451</v>
+        <v>13317.47423389435</v>
       </c>
       <c r="D158" t="n">
-        <v>14284.10569726401</v>
+        <v>14393.07365617827</v>
       </c>
       <c r="E158" t="n">
-        <v>15376.56700955972</v>
+        <v>15749.26460127504</v>
       </c>
       <c r="F158" t="n">
-        <v>16515.84691797099</v>
+        <v>16587.48551255381</v>
       </c>
       <c r="G158" t="n">
-        <v>12637.67110790988</v>
+        <v>12684.32439257352</v>
       </c>
       <c r="H158" t="n">
-        <v>13624.84065521619</v>
+        <v>13545.97368176006</v>
       </c>
       <c r="I158" t="n">
-        <v>14481.07049923271</v>
+        <v>14494.51386450879</v>
       </c>
       <c r="J158" t="n">
-        <v>15446.72709702502</v>
+        <v>15478.82778152398</v>
       </c>
       <c r="K158" t="n">
-        <v>13453.74416254383</v>
+        <v>13220.75970307931</v>
       </c>
       <c r="L158" t="n">
-        <v>14424.28095403771</v>
+        <v>14384.89863730358</v>
       </c>
       <c r="M158" t="n">
-        <v>15512.74129795585</v>
+        <v>15379.73371026167</v>
       </c>
       <c r="N158" t="n">
-        <v>16589.33835456199</v>
+        <v>16553.51099992081</v>
       </c>
       <c r="O158" t="n">
-        <v>12890.36682454054</v>
+        <v>12820.89988707604</v>
       </c>
       <c r="P158" t="n">
-        <v>13822.87632702221</v>
+        <v>13817.05345937718</v>
       </c>
       <c r="Q158" t="n">
-        <v>14962.87513822203</v>
+        <v>14889.83707263042</v>
       </c>
       <c r="R158" t="n">
-        <v>16185.48056081298</v>
+        <v>15965.22566442684</v>
       </c>
       <c r="S158" t="n">
-        <v>12334.88762374707</v>
+        <v>12460.69562726881</v>
       </c>
       <c r="T158" t="n">
-        <v>13257.81019264022</v>
+        <v>13239.25378666824</v>
       </c>
       <c r="U158" t="n">
-        <v>14333.47291854086</v>
+        <v>14214.53594722342</v>
       </c>
       <c r="V158" t="n">
-        <v>15306.54040184268</v>
+        <v>15241.98844432263</v>
       </c>
       <c r="W158" t="n">
-        <v>12305.18600742801</v>
+        <v>12343.84871661541</v>
       </c>
       <c r="X158" t="n">
-        <v>13283.54115124964</v>
+        <v>13242.43086767112</v>
       </c>
       <c r="Y158" t="n">
-        <v>14371.09108615735</v>
+        <v>14341.9953530914</v>
       </c>
       <c r="Z158" t="n">
-        <v>15229.12044074108</v>
+        <v>15519.15503166635</v>
       </c>
     </row>
     <row r="159">
@@ -14296,76 +14296,76 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>12766.84518582451</v>
+        <v>12917.47423389435</v>
       </c>
       <c r="D159" t="n">
-        <v>13884.10569726401</v>
+        <v>13993.07365617827</v>
       </c>
       <c r="E159" t="n">
-        <v>14976.56700955972</v>
+        <v>15349.26460127504</v>
       </c>
       <c r="F159" t="n">
-        <v>16115.84691797099</v>
+        <v>16187.48551255381</v>
       </c>
       <c r="G159" t="n">
-        <v>12237.67110790988</v>
+        <v>12284.32439257352</v>
       </c>
       <c r="H159" t="n">
-        <v>13224.84065521619</v>
+        <v>13145.97368176006</v>
       </c>
       <c r="I159" t="n">
-        <v>14081.07049923271</v>
+        <v>14094.51386450879</v>
       </c>
       <c r="J159" t="n">
-        <v>15046.72709702502</v>
+        <v>15078.82778152398</v>
       </c>
       <c r="K159" t="n">
-        <v>13053.74416254383</v>
+        <v>12820.75970307931</v>
       </c>
       <c r="L159" t="n">
-        <v>14024.28095403771</v>
+        <v>13984.89863730358</v>
       </c>
       <c r="M159" t="n">
-        <v>15112.74129795585</v>
+        <v>14979.73371026167</v>
       </c>
       <c r="N159" t="n">
-        <v>16189.33835456199</v>
+        <v>16153.51099992081</v>
       </c>
       <c r="O159" t="n">
-        <v>12490.36682454054</v>
+        <v>12420.89988707604</v>
       </c>
       <c r="P159" t="n">
-        <v>13422.87632702221</v>
+        <v>13417.05345937718</v>
       </c>
       <c r="Q159" t="n">
-        <v>14562.87513822203</v>
+        <v>14489.83707263042</v>
       </c>
       <c r="R159" t="n">
-        <v>15785.48056081298</v>
+        <v>15565.22566442684</v>
       </c>
       <c r="S159" t="n">
-        <v>11934.88762374707</v>
+        <v>12060.69562726881</v>
       </c>
       <c r="T159" t="n">
-        <v>12857.81019264022</v>
+        <v>12839.25378666824</v>
       </c>
       <c r="U159" t="n">
-        <v>13933.47291854086</v>
+        <v>13814.53594722342</v>
       </c>
       <c r="V159" t="n">
-        <v>14906.54040184268</v>
+        <v>14841.98844432263</v>
       </c>
       <c r="W159" t="n">
-        <v>11905.18600742801</v>
+        <v>11943.84871661541</v>
       </c>
       <c r="X159" t="n">
-        <v>12883.54115124964</v>
+        <v>12842.43086767112</v>
       </c>
       <c r="Y159" t="n">
-        <v>13971.09108615735</v>
+        <v>13941.9953530914</v>
       </c>
       <c r="Z159" t="n">
-        <v>14829.12044074108</v>
+        <v>15119.15503166635</v>
       </c>
     </row>
     <row r="160">
@@ -14378,76 +14378,76 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>1276.684518582451</v>
+        <v>1291.747423389435</v>
       </c>
       <c r="D160" t="n">
-        <v>1388.410569726401</v>
+        <v>1399.307365617826</v>
       </c>
       <c r="E160" t="n">
-        <v>1497.656700955972</v>
+        <v>1534.926460127504</v>
       </c>
       <c r="F160" t="n">
-        <v>1611.584691797099</v>
+        <v>1618.748551255381</v>
       </c>
       <c r="G160" t="n">
-        <v>1223.767110790988</v>
+        <v>1228.432439257352</v>
       </c>
       <c r="H160" t="n">
-        <v>1322.484065521619</v>
+        <v>1314.597368176006</v>
       </c>
       <c r="I160" t="n">
-        <v>1408.107049923271</v>
+        <v>1409.451386450879</v>
       </c>
       <c r="J160" t="n">
-        <v>1504.672709702502</v>
+        <v>1507.882778152398</v>
       </c>
       <c r="K160" t="n">
-        <v>1305.374416254383</v>
+        <v>1282.075970307931</v>
       </c>
       <c r="L160" t="n">
-        <v>1402.428095403771</v>
+        <v>1398.489863730358</v>
       </c>
       <c r="M160" t="n">
-        <v>1511.274129795585</v>
+        <v>1497.973371026167</v>
       </c>
       <c r="N160" t="n">
-        <v>1618.933835456199</v>
+        <v>1615.35109999208</v>
       </c>
       <c r="O160" t="n">
-        <v>1249.036682454054</v>
+        <v>1242.089988707603</v>
       </c>
       <c r="P160" t="n">
-        <v>1342.287632702221</v>
+        <v>1341.705345937718</v>
       </c>
       <c r="Q160" t="n">
-        <v>1456.287513822203</v>
+        <v>1448.983707263042</v>
       </c>
       <c r="R160" t="n">
-        <v>1578.548056081298</v>
+        <v>1556.522566442684</v>
       </c>
       <c r="S160" t="n">
-        <v>1193.488762374707</v>
+        <v>1206.069562726881</v>
       </c>
       <c r="T160" t="n">
-        <v>1285.781019264022</v>
+        <v>1283.925378666824</v>
       </c>
       <c r="U160" t="n">
-        <v>1393.347291854086</v>
+        <v>1381.453594722342</v>
       </c>
       <c r="V160" t="n">
-        <v>1490.654040184268</v>
+        <v>1484.198844432263</v>
       </c>
       <c r="W160" t="n">
-        <v>1190.518600742801</v>
+        <v>1194.384871661541</v>
       </c>
       <c r="X160" t="n">
-        <v>1288.354115124964</v>
+        <v>1284.243086767112</v>
       </c>
       <c r="Y160" t="n">
-        <v>1397.109108615735</v>
+        <v>1394.19953530914</v>
       </c>
       <c r="Z160" t="n">
-        <v>1482.912044074108</v>
+        <v>1511.915503166636</v>
       </c>
     </row>
     <row r="161">
@@ -14706,76 +14706,76 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>39988.1014870634</v>
+        <v>39182.82057430764</v>
       </c>
       <c r="D164" t="n">
-        <v>42117.94054969586</v>
+        <v>41589.01362037759</v>
       </c>
       <c r="E164" t="n">
-        <v>44559.26555390007</v>
+        <v>42977.05694398365</v>
       </c>
       <c r="F164" t="n">
-        <v>46978.67901110116</v>
+        <v>46700.00547863517</v>
       </c>
       <c r="G164" t="n">
-        <v>42797.87736381706</v>
+        <v>42565.63546498946</v>
       </c>
       <c r="H164" t="n">
-        <v>45198.83308111294</v>
+        <v>45548.83646277965</v>
       </c>
       <c r="I164" t="n">
-        <v>48261.37150968693</v>
+        <v>48215.42009143704</v>
       </c>
       <c r="J164" t="n">
-        <v>50932.55744645447</v>
+        <v>50825.9053685645</v>
       </c>
       <c r="K164" t="n">
-        <v>40366.10585902184</v>
+        <v>41464.79179952629</v>
       </c>
       <c r="L164" t="n">
-        <v>43345.98317596801</v>
+        <v>43503.56682839447</v>
       </c>
       <c r="M164" t="n">
-        <v>45948.21112450033</v>
+        <v>46407.9623835232</v>
       </c>
       <c r="N164" t="n">
-        <v>48680.43127879095</v>
+        <v>48795.50370893543</v>
       </c>
       <c r="O164" t="n">
-        <v>42821.75410092968</v>
+        <v>43088.14533650997</v>
       </c>
       <c r="P164" t="n">
-        <v>45656.08448147578</v>
+        <v>45591.52189790158</v>
       </c>
       <c r="Q164" t="n">
-        <v>47760.95245551236</v>
+        <v>47973.35931176611</v>
       </c>
       <c r="R164" t="n">
-        <v>49917.7328042869</v>
+        <v>50482.40518958342</v>
       </c>
       <c r="S164" t="n">
-        <v>44263.27439894858</v>
+        <v>43675.68508424639</v>
       </c>
       <c r="T164" t="n">
-        <v>46737.16001056239</v>
+        <v>46816.01786802559</v>
       </c>
       <c r="U164" t="n">
-        <v>48803.96040720643</v>
+        <v>49212.14942398232</v>
       </c>
       <c r="V164" t="n">
-        <v>51386.54059596502</v>
+        <v>51577.23699349092</v>
       </c>
       <c r="W164" t="n">
-        <v>44474.00696681895</v>
+        <v>44216.60579358091</v>
       </c>
       <c r="X164" t="n">
-        <v>46638.50370369997</v>
+        <v>46854.80365120493</v>
       </c>
       <c r="Y164" t="n">
-        <v>48669.09251125647</v>
+        <v>48773.63080002777</v>
       </c>
       <c r="Z164" t="n">
-        <v>51615.41307178741</v>
+        <v>50690.08162526663</v>
       </c>
     </row>
     <row r="165">
@@ -14870,76 +14870,76 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>143439.3075064732</v>
+        <v>144964.4266181802</v>
       </c>
       <c r="D166" t="n">
-        <v>191051.3212158001</v>
+        <v>192413.4207022283</v>
       </c>
       <c r="E166" t="n">
-        <v>247695.5760195907</v>
+        <v>253332.627094285</v>
       </c>
       <c r="F166" t="n">
-        <v>315285.2445234779</v>
+        <v>316574.7392259685</v>
       </c>
       <c r="G166" t="n">
-        <v>138081.4199675876</v>
+        <v>138553.7844748069</v>
       </c>
       <c r="H166" t="n">
-        <v>182810.5081902023</v>
+        <v>181824.6710220008</v>
       </c>
       <c r="I166" t="n">
-        <v>234151.1913008947</v>
+        <v>234354.5222006954</v>
       </c>
       <c r="J166" t="n">
-        <v>296041.0877464503</v>
+        <v>296618.9000674316</v>
       </c>
       <c r="K166" t="n">
-        <v>146344.1596457563</v>
+        <v>143985.191993678</v>
       </c>
       <c r="L166" t="n">
-        <v>192803.5119254714</v>
+        <v>192311.2329662947</v>
       </c>
       <c r="M166" t="n">
-        <v>249755.2121315822</v>
+        <v>247743.4723677078</v>
       </c>
       <c r="N166" t="n">
-        <v>316608.0903821158</v>
+        <v>315963.1979985745</v>
       </c>
       <c r="O166" t="n">
-        <v>140639.9640984729</v>
+        <v>139936.6113566449</v>
       </c>
       <c r="P166" t="n">
-        <v>185285.9540877776</v>
+        <v>185213.1682422147</v>
       </c>
       <c r="Q166" t="n">
-        <v>241438.4864656083</v>
+        <v>240333.7857235351</v>
       </c>
       <c r="R166" t="n">
-        <v>309338.6500946336</v>
+        <v>305374.061959683</v>
       </c>
       <c r="S166" t="n">
-        <v>135015.7371904391</v>
+        <v>136289.5432260968</v>
       </c>
       <c r="T166" t="n">
-        <v>178222.6274080028</v>
+        <v>177990.6723333529</v>
       </c>
       <c r="U166" t="n">
-        <v>231918.7778929304</v>
+        <v>230119.8562017542</v>
       </c>
       <c r="V166" t="n">
-        <v>293517.7272331683</v>
+        <v>292355.7919978074</v>
       </c>
       <c r="W166" t="n">
-        <v>134715.0083252086</v>
+        <v>135106.468255731</v>
       </c>
       <c r="X166" t="n">
-        <v>178544.2643906205</v>
+        <v>178030.385845889</v>
       </c>
       <c r="Y166" t="n">
-        <v>232487.7526781299</v>
+        <v>232047.6797155075</v>
       </c>
       <c r="Z166" t="n">
-        <v>292124.1679333394</v>
+        <v>297344.7905699944</v>
       </c>
     </row>
     <row r="167">
@@ -15083,122 +15083,122 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE2F7B0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFE2FD70360&gt;</t>
         </is>
       </c>
     </row>
@@ -21390,76 +21390,76 @@
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>0.02187908610561249</v>
+        <v>0.02096179656180743</v>
       </c>
       <c r="D218" t="n">
-        <v>0.02472818189394919</v>
+        <v>0.0240683499014966</v>
       </c>
       <c r="E218" t="n">
-        <v>0.02800683890934326</v>
+        <v>0.02582970022864849</v>
       </c>
       <c r="F218" t="n">
-        <v>0.03125844055999591</v>
+        <v>0.03082033315301926</v>
       </c>
       <c r="G218" t="n">
-        <v>0.02561349431998408</v>
+        <v>0.02524819881764313</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0293504736219936</v>
+        <v>0.02998684488446704</v>
       </c>
       <c r="I218" t="n">
-        <v>0.03448572298723581</v>
+        <v>0.03437280925203347</v>
       </c>
       <c r="J218" t="n">
-        <v>0.03905698597055748</v>
+        <v>0.03878292737959663</v>
       </c>
       <c r="K218" t="n">
-        <v>0.02144091005228463</v>
+        <v>0.02289063198808505</v>
       </c>
       <c r="L218" t="n">
-        <v>0.02537690413046488</v>
+        <v>0.02562425827634892</v>
       </c>
       <c r="M218" t="n">
-        <v>0.02887988554201509</v>
+        <v>0.02973641974761076</v>
       </c>
       <c r="N218" t="n">
-        <v>0.03273469272485669</v>
+        <v>0.03296615286522218</v>
       </c>
       <c r="O218" t="n">
-        <v>0.02520533207029557</v>
+        <v>0.0257354101865097</v>
       </c>
       <c r="P218" t="n">
-        <v>0.02957707180768901</v>
+        <v>0.02962259331534554</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.03267723363362485</v>
+        <v>0.03323630536045696</v>
       </c>
       <c r="R218" t="n">
-        <v>0.03549033960016711</v>
+        <v>0.03713964449532495</v>
       </c>
       <c r="S218" t="n">
-        <v>0.02818340469190036</v>
+        <v>0.02707179548783295</v>
       </c>
       <c r="T218" t="n">
-        <v>0.03249241298332263</v>
+        <v>0.03266415545088044</v>
       </c>
       <c r="U218" t="n">
-        <v>0.03576210419939551</v>
+        <v>0.03684178586229331</v>
       </c>
       <c r="V218" t="n">
-        <v>0.04028789090728659</v>
+        <v>0.04087397076793777</v>
       </c>
       <c r="W218" t="n">
-        <v>0.02845555528472285</v>
+        <v>0.02810204194621242</v>
       </c>
       <c r="X218" t="n">
-        <v>0.03225644925831661</v>
+        <v>0.03263465687682106</v>
       </c>
       <c r="Y218" t="n">
-        <v>0.03543028369468331</v>
+        <v>0.03568653110677272</v>
       </c>
       <c r="Z218" t="n">
-        <v>0.04099230148008643</v>
+        <v>0.03844263145893523</v>
       </c>
     </row>
     <row r="219">
@@ -21472,76 +21472,76 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>0.01997124016358967</v>
+        <v>0.02041163333027671</v>
       </c>
       <c r="D219" t="n">
-        <v>0.02189553286669016</v>
+        <v>0.02222098771109266</v>
       </c>
       <c r="E219" t="n">
-        <v>0.02362092396188654</v>
+        <v>0.02467229553800216</v>
       </c>
       <c r="F219" t="n">
-        <v>0.02534507371691141</v>
+        <v>0.0255582347753803</v>
       </c>
       <c r="G219" t="n">
-        <v>0.01817312531557474</v>
+        <v>0.01834447517990977</v>
       </c>
       <c r="H219" t="n">
-        <v>0.01967267443587358</v>
+        <v>0.01936532387597433</v>
       </c>
       <c r="I219" t="n">
-        <v>0.02048758812763831</v>
+        <v>0.02053876993607843</v>
       </c>
       <c r="J219" t="n">
-        <v>0.02156716350105954</v>
+        <v>0.02170007206066392</v>
       </c>
       <c r="K219" t="n">
-        <v>0.02016465238271574</v>
+        <v>0.01944377744451516</v>
       </c>
       <c r="L219" t="n">
-        <v>0.02157384577240922</v>
+        <v>0.02145452398329767</v>
       </c>
       <c r="M219" t="n">
-        <v>0.02317671393468264</v>
+        <v>0.02276732518881927</v>
       </c>
       <c r="N219" t="n">
-        <v>0.02461262549993926</v>
+        <v>0.02449848803773205</v>
       </c>
       <c r="O219" t="n">
-        <v>0.01835443098229396</v>
+        <v>0.01809892702020569</v>
       </c>
       <c r="P219" t="n">
-        <v>0.01948612082733887</v>
+        <v>0.01952132912438591</v>
       </c>
       <c r="Q219" t="n">
-        <v>0.02134449757158811</v>
+        <v>0.02107387582085563</v>
       </c>
       <c r="R219" t="n">
-        <v>0.02325507773146714</v>
+        <v>0.0224698243097472</v>
       </c>
       <c r="S219" t="n">
-        <v>0.01693002953672349</v>
+        <v>0.01747040297853972</v>
       </c>
       <c r="T219" t="n">
-        <v>0.01815463273987319</v>
+        <v>0.01806572307795161</v>
       </c>
       <c r="U219" t="n">
-        <v>0.01986965925650698</v>
+        <v>0.01934682754869307</v>
       </c>
       <c r="V219" t="n">
-        <v>0.0209663210557778</v>
+        <v>0.02068581735662994</v>
       </c>
       <c r="W219" t="n">
-        <v>0.01674784673518851</v>
+        <v>0.0169735737840696</v>
       </c>
       <c r="X219" t="n">
-        <v>0.01826868628132749</v>
+        <v>0.01804618696049168</v>
       </c>
       <c r="Y219" t="n">
-        <v>0.02003032179554441</v>
+        <v>0.01990625092508599</v>
       </c>
       <c r="Z219" t="n">
-        <v>0.02062840917987342</v>
+        <v>0.02186509760819577</v>
       </c>
     </row>
     <row r="220">
@@ -21554,76 +21554,76 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>0.0008436549442855587</v>
+        <v>0.0007990027724866452</v>
       </c>
       <c r="D220" t="n">
-        <v>0.0008778754727306865</v>
+        <v>0.0008478906854337226</v>
       </c>
       <c r="E220" t="n">
-        <v>0.0009227000708296464</v>
+        <v>0.0008305762648907026</v>
       </c>
       <c r="F220" t="n">
-        <v>0.000957916580032586</v>
+        <v>0.0009403618733761525</v>
       </c>
       <c r="G220" t="n">
-        <v>0.001029674048210476</v>
+        <v>0.001011196041680172</v>
       </c>
       <c r="H220" t="n">
-        <v>0.001093140483965058</v>
+        <v>0.001123441631143408</v>
       </c>
       <c r="I220" t="n">
-        <v>0.001207392785754004</v>
+        <v>0.00120230773770405</v>
       </c>
       <c r="J220" t="n">
-        <v>0.001280831804819881</v>
+        <v>0.001269172214457942</v>
       </c>
       <c r="K220" t="n">
-        <v>0.0008088623784092045</v>
+        <v>0.0008790052389443751</v>
       </c>
       <c r="L220" t="n">
-        <v>0.0008920276607465834</v>
+        <v>0.0009032231717525993</v>
       </c>
       <c r="M220" t="n">
-        <v>0.0009430018107166211</v>
+        <v>0.0009794776481325427</v>
       </c>
       <c r="N220" t="n">
-        <v>0.0009986581525344158</v>
+        <v>0.001007922789955682</v>
       </c>
       <c r="O220" t="n">
-        <v>0.0009930891840554872</v>
+        <v>0.001019555278021938</v>
       </c>
       <c r="P220" t="n">
-        <v>0.001085566333338144</v>
+        <v>0.001087702027597842</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.001106736774770295</v>
+        <v>0.001131268685831161</v>
       </c>
       <c r="R220" t="n">
-        <v>0.001110080471624</v>
+        <v>0.001177897649100198</v>
       </c>
       <c r="S220" t="n">
-        <v>0.001161255281703126</v>
+        <v>0.001104007321885677</v>
       </c>
       <c r="T220" t="n">
-        <v>0.0012441754208388</v>
+        <v>0.001252531624327972</v>
       </c>
       <c r="U220" t="n">
-        <v>0.001265156285560973</v>
+        <v>0.001314413334877223</v>
       </c>
       <c r="V220" t="n">
-        <v>0.001333458549595257</v>
+        <v>0.001358662483993764</v>
       </c>
       <c r="W220" t="n">
-        <v>0.001175345643894356</v>
+        <v>0.001157048420232819</v>
       </c>
       <c r="X220" t="n">
-        <v>0.001232710964310902</v>
+        <v>0.001251095643439986</v>
       </c>
       <c r="Y220" t="n">
-        <v>0.001250090182868574</v>
+        <v>0.001261721921686664</v>
       </c>
       <c r="Z220" t="n">
-        <v>0.001363762491681287</v>
+        <v>0.001254724277529346</v>
       </c>
     </row>
     <row r="221">
@@ -21636,76 +21636,76 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>0.0007420536264727845</v>
+        <v>0.0007333846872340609</v>
       </c>
       <c r="D221" t="n">
-        <v>0.000757990370806288</v>
+        <v>0.0007522518525477197</v>
       </c>
       <c r="E221" t="n">
-        <v>0.0007731376014047612</v>
+        <v>0.0007543649347129221</v>
       </c>
       <c r="F221" t="n">
-        <v>0.0007837777342662148</v>
+        <v>0.0007803298821065839</v>
       </c>
       <c r="G221" t="n">
-        <v>0.0007741359854956435</v>
+        <v>0.0007710791315136365</v>
       </c>
       <c r="H221" t="n">
-        <v>0.0007959502815292954</v>
+        <v>0.0008007254386758437</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0008223058683328882</v>
+        <v>0.0008214454280567662</v>
       </c>
       <c r="J221" t="n">
-        <v>0.0008394901338503862</v>
+        <v>0.0008377029443864749</v>
       </c>
       <c r="K221" t="n">
-        <v>0.0007256876741071349</v>
+        <v>0.0007383167610216868</v>
       </c>
       <c r="L221" t="n">
-        <v>0.0007505775140025316</v>
+        <v>0.000752691240911216</v>
       </c>
       <c r="M221" t="n">
-        <v>0.0007660733474037228</v>
+        <v>0.0007729741520356404</v>
       </c>
       <c r="N221" t="n">
-        <v>0.0007802405854437597</v>
+        <v>0.0007819329311535415</v>
       </c>
       <c r="O221" t="n">
-        <v>0.0007584792599419226</v>
+        <v>0.0007627212391536818</v>
       </c>
       <c r="P221" t="n">
-        <v>0.0007828281058473338</v>
+        <v>0.0007844832208641293</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.0007951003670924816</v>
+        <v>0.0007991081807215928</v>
       </c>
       <c r="R221" t="n">
-        <v>0.0007997714599994055</v>
+        <v>0.0008113772790188546</v>
       </c>
       <c r="S221" t="n">
-        <v>0.0007936699227177019</v>
+        <v>0.0007855006109178637</v>
       </c>
       <c r="T221" t="n">
-        <v>0.0008186709546462937</v>
+        <v>0.0008197127092400487</v>
       </c>
       <c r="U221" t="n">
-        <v>0.0008310165352371102</v>
+        <v>0.0008381712834448894</v>
       </c>
       <c r="V221" t="n">
-        <v>0.0008473059705566261</v>
+        <v>0.0008510705224412377</v>
       </c>
       <c r="W221" t="n">
-        <v>0.0007943346075583758</v>
+        <v>0.0007931852112077964</v>
       </c>
       <c r="X221" t="n">
-        <v>0.0008170358990090179</v>
+        <v>0.000818698851010036</v>
       </c>
       <c r="Y221" t="n">
-        <v>0.0008287790315021458</v>
+        <v>0.000830508552634052</v>
       </c>
       <c r="Z221" t="n">
-        <v>0.0008518090129028764</v>
+        <v>0.0008354685755532495</v>
       </c>
     </row>
     <row r="222">
@@ -21718,76 +21718,76 @@
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>0.0323124361918474</v>
+        <v>0.03096329317921915</v>
       </c>
       <c r="D222" t="n">
-        <v>0.03656554755728537</v>
+        <v>0.03559379044098467</v>
       </c>
       <c r="E222" t="n">
-        <v>0.04145663832151709</v>
+        <v>0.03824620458403832</v>
       </c>
       <c r="F222" t="n">
-        <v>0.04631291089197431</v>
+        <v>0.04566628260550319</v>
       </c>
       <c r="G222" t="n">
-        <v>0.03780243705104984</v>
+        <v>0.03726558060145659</v>
       </c>
       <c r="H222" t="n">
-        <v>0.04336982614261137</v>
+        <v>0.04430620234801451</v>
       </c>
       <c r="I222" t="n">
-        <v>0.05100414880940131</v>
+        <v>0.05083782923542778</v>
       </c>
       <c r="J222" t="n">
-        <v>0.0578169798729443</v>
+        <v>0.05741288774072018</v>
       </c>
       <c r="K222" t="n">
-        <v>0.03167604765138142</v>
+        <v>0.03380854483876095</v>
       </c>
       <c r="L222" t="n">
-        <v>0.03753013959924936</v>
+        <v>0.03789445351147182</v>
       </c>
       <c r="M222" t="n">
-        <v>0.04275402722659267</v>
+        <v>0.04401694303253661</v>
       </c>
       <c r="N222" t="n">
-        <v>0.04850284419576439</v>
+        <v>0.04884447562385985</v>
       </c>
       <c r="O222" t="n">
-        <v>0.03721214459501007</v>
+        <v>0.03799138211295138</v>
       </c>
       <c r="P222" t="n">
-        <v>0.04371426791153062</v>
+        <v>0.04378126875645961</v>
       </c>
       <c r="Q222" t="n">
-        <v>0.04835180838557509</v>
+        <v>0.04917569682918675</v>
       </c>
       <c r="R222" t="n">
-        <v>0.05256946111727626</v>
+        <v>0.0550027281535273</v>
       </c>
       <c r="S222" t="n">
-        <v>0.04157835386882866</v>
+        <v>0.03994528883861802</v>
       </c>
       <c r="T222" t="n">
-        <v>0.04799211422248066</v>
+        <v>0.04824471420172387</v>
       </c>
       <c r="U222" t="n">
-        <v>0.05288406252775668</v>
+        <v>0.05447403079251364</v>
       </c>
       <c r="V222" t="n">
-        <v>0.05963176123117274</v>
+        <v>0.0604957586615104</v>
       </c>
       <c r="W222" t="n">
-        <v>0.04197812554074766</v>
+        <v>0.04145883386717894</v>
       </c>
       <c r="X222" t="n">
-        <v>0.04764504730888838</v>
+        <v>0.0482013279291676</v>
       </c>
       <c r="Y222" t="n">
-        <v>0.05239537143230383</v>
+        <v>0.05277276350714707</v>
       </c>
       <c r="Z222" t="n">
-        <v>0.06067019472512087</v>
+        <v>0.05691111262188523</v>
       </c>
     </row>
     <row r="223">
@@ -21800,76 +21800,76 @@
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>0.02999999860106601</v>
+        <v>0.02999934636944903</v>
       </c>
       <c r="D223" t="n">
-        <v>0.03332605834831233</v>
+        <v>0.03333333267220651</v>
       </c>
       <c r="E223" t="n">
-        <v>0.03666666580098748</v>
+        <v>0.03666666546463534</v>
       </c>
       <c r="F223" t="n">
-        <v>0.03999893294663663</v>
+        <v>0.03999999909510812</v>
       </c>
       <c r="G223" t="n">
-        <v>0.02999980168042904</v>
+        <v>0.02999525624888166</v>
       </c>
       <c r="H223" t="n">
-        <v>0.03333333286854807</v>
+        <v>0.03333333255330332</v>
       </c>
       <c r="I223" t="n">
-        <v>0.03666666519577253</v>
+        <v>0.03666326758649759</v>
       </c>
       <c r="J223" t="n">
-        <v>0.03999999999152393</v>
+        <v>0.03999999836318417</v>
       </c>
       <c r="K223" t="n">
-        <v>0.02999764725906907</v>
+        <v>0.02997497562974712</v>
       </c>
       <c r="L223" t="n">
-        <v>0.03333331479148981</v>
+        <v>0.0333333172462104</v>
       </c>
       <c r="M223" t="n">
-        <v>0.03666198299614314</v>
+        <v>0.0366666653809625</v>
       </c>
       <c r="N223" t="n">
-        <v>0.03999999964641696</v>
+        <v>0.03999804698119847</v>
       </c>
       <c r="O223" t="n">
-        <v>0.02999999992068872</v>
+        <v>0.02999999981870246</v>
       </c>
       <c r="P223" t="n">
-        <v>0.03327471535866841</v>
+        <v>0.03333060215567498</v>
       </c>
       <c r="Q223" t="n">
-        <v>0.03666666666635399</v>
+        <v>0.03666666658319628</v>
       </c>
       <c r="R223" t="n">
-        <v>0.03997845997722649</v>
+        <v>0.03999268974857077</v>
       </c>
       <c r="S223" t="n">
-        <v>0.02999581090361535</v>
+        <v>0.0299999986471612</v>
       </c>
       <c r="T223" t="n">
-        <v>0.03333333319272045</v>
+        <v>0.03332758176928619</v>
       </c>
       <c r="U223" t="n">
-        <v>0.03666666356385544</v>
+        <v>0.0366666665294194</v>
       </c>
       <c r="V223" t="n">
-        <v>0.03999626882894542</v>
+        <v>0.03999999972135884</v>
       </c>
       <c r="W223" t="n">
-        <v>0.02994622064121269</v>
+        <v>0.02999999986192145</v>
       </c>
       <c r="X223" t="n">
-        <v>0.03333333281861459</v>
+        <v>0.03329459741920417</v>
       </c>
       <c r="Y223" t="n">
-        <v>0.0366666665748102</v>
+        <v>0.03666666354150096</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.0399999984086775</v>
+        <v>0.03999999990660427</v>
       </c>
     </row>
     <row r="224">
@@ -21882,76 +21882,76 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>982.1986475690828</v>
+        <v>982.0115041248142</v>
       </c>
       <c r="D224" t="n">
-        <v>1192.410247585297</v>
+        <v>1192.36393718622</v>
       </c>
       <c r="E224" t="n">
-        <v>1427.093577749882</v>
+        <v>1428.668608653932</v>
       </c>
       <c r="F224" t="n">
-        <v>1687.357335415434</v>
+        <v>1687.394630005742</v>
       </c>
       <c r="G224" t="n">
-        <v>892.5006152018994</v>
+        <v>892.6681312428833</v>
       </c>
       <c r="H224" t="n">
-        <v>1078.96433529275</v>
+        <v>1078.783919161895</v>
       </c>
       <c r="I224" t="n">
-        <v>1286.008190687583</v>
+        <v>1286.043704652937</v>
       </c>
       <c r="J224" t="n">
-        <v>1515.029491434301</v>
+        <v>1515.011329695099</v>
       </c>
       <c r="K224" t="n">
-        <v>1030.04338981346</v>
+        <v>1030.365440264962</v>
       </c>
       <c r="L224" t="n">
-        <v>1252.739120339443</v>
+        <v>1252.739176641298</v>
       </c>
       <c r="M224" t="n">
-        <v>1501.909124679483</v>
+        <v>1502.061845601484</v>
       </c>
       <c r="N224" t="n">
-        <v>1778.301658899254</v>
+        <v>1778.383733016381</v>
       </c>
       <c r="O224" t="n">
-        <v>937.8398426647824</v>
+        <v>937.2965928936544</v>
       </c>
       <c r="P224" t="n">
-        <v>1135.982813898963</v>
+        <v>1135.445938805105</v>
       </c>
       <c r="Q224" t="n">
-        <v>1357.430338821005</v>
+        <v>1356.565237431589</v>
       </c>
       <c r="R224" t="n">
-        <v>1604.647989472047</v>
+        <v>1601.089984052448</v>
       </c>
       <c r="S224" t="n">
-        <v>1352.300773759447</v>
+        <v>1353.618075773677</v>
       </c>
       <c r="T224" t="n">
-        <v>1654.460282606412</v>
+        <v>1654.388861214288</v>
       </c>
       <c r="U224" t="n">
-        <v>1994.827784381827</v>
+        <v>1993.056589170385</v>
       </c>
       <c r="V224" t="n">
-        <v>2371.348406845296</v>
+        <v>2370.118274426763</v>
       </c>
       <c r="W224" t="n">
-        <v>1244.613232116085</v>
+        <v>1245.761868806949</v>
       </c>
       <c r="X224" t="n">
-        <v>1520.761041904493</v>
+        <v>1519.175130544477</v>
       </c>
       <c r="Y224" t="n">
-        <v>1834.964185875724</v>
+        <v>1833.271995354124</v>
       </c>
       <c r="Z224" t="n">
-        <v>2168.262886786363</v>
+        <v>2187.01949127484</v>
       </c>
     </row>
     <row r="225">
@@ -21964,76 +21964,76 @@
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>17.53997745948471</v>
+        <v>17.53685840208023</v>
       </c>
       <c r="D225" t="n">
-        <v>21.17350412642161</v>
+        <v>21.17273228643699</v>
       </c>
       <c r="E225" t="n">
-        <v>25.21489296249803</v>
+        <v>25.24114347756553</v>
       </c>
       <c r="F225" t="n">
-        <v>29.6826222569239</v>
+        <v>29.68324383342904</v>
       </c>
       <c r="G225" t="n">
-        <v>16.04501025336499</v>
+        <v>16.04780218738139</v>
       </c>
       <c r="H225" t="n">
-        <v>19.28273892154584</v>
+        <v>19.27973198603159</v>
       </c>
       <c r="I225" t="n">
-        <v>22.86346984479305</v>
+        <v>22.86406174421561</v>
       </c>
       <c r="J225" t="n">
-        <v>26.81049152390502</v>
+        <v>26.81018882825165</v>
       </c>
       <c r="K225" t="n">
-        <v>18.33738983022433</v>
+        <v>18.34275733774937</v>
       </c>
       <c r="L225" t="n">
-        <v>22.17898533899071</v>
+        <v>22.17898627735497</v>
       </c>
       <c r="M225" t="n">
-        <v>26.46181874465804</v>
+        <v>26.46436409335806</v>
       </c>
       <c r="N225" t="n">
-        <v>31.19836098165423</v>
+        <v>31.19972888360636</v>
       </c>
       <c r="O225" t="n">
-        <v>16.80066404441304</v>
+        <v>16.79160988156091</v>
       </c>
       <c r="P225" t="n">
-        <v>20.23304689831605</v>
+        <v>20.22409898008508</v>
       </c>
       <c r="Q225" t="n">
-        <v>24.05383898035009</v>
+        <v>24.03942062385982</v>
       </c>
       <c r="R225" t="n">
-        <v>28.30413315786745</v>
+        <v>28.2448330675408</v>
       </c>
       <c r="S225" t="n">
-        <v>23.70834622932411</v>
+        <v>23.73030126289461</v>
       </c>
       <c r="T225" t="n">
-        <v>28.8743380434402</v>
+        <v>28.8731476869048</v>
       </c>
       <c r="U225" t="n">
-        <v>34.67712973969711</v>
+        <v>34.64760981950641</v>
       </c>
       <c r="V225" t="n">
-        <v>41.08247344742161</v>
+        <v>41.06197124044604</v>
       </c>
       <c r="W225" t="n">
-        <v>21.91355386860141</v>
+        <v>21.93269781344914</v>
       </c>
       <c r="X225" t="n">
-        <v>26.64601736507488</v>
+        <v>26.61958550907461</v>
       </c>
       <c r="Y225" t="n">
-        <v>32.01273643126206</v>
+        <v>31.98453325590207</v>
       </c>
       <c r="Z225" t="n">
-        <v>37.69771477977271</v>
+        <v>38.01032485458066</v>
       </c>
     </row>
     <row r="226">
@@ -22046,76 +22046,76 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>3.683068707942869</v>
+        <v>3.683108745495228</v>
       </c>
       <c r="D226" t="n">
-        <v>3.494447038888318</v>
+        <v>3.494065721982071</v>
       </c>
       <c r="E226" t="n">
-        <v>3.331460956564474</v>
+        <v>3.33146097184462</v>
       </c>
       <c r="F226" t="n">
-        <v>3.189673535276158</v>
+        <v>3.189631026672389</v>
       </c>
       <c r="G226" t="n">
-        <v>3.683080795873542</v>
+        <v>3.683359849289807</v>
       </c>
       <c r="H226" t="n">
-        <v>3.494065711691616</v>
+        <v>3.494065728213905</v>
       </c>
       <c r="I226" t="n">
-        <v>3.331460984058793</v>
+        <v>3.331615344829953</v>
       </c>
       <c r="J226" t="n">
-        <v>3.189630990931942</v>
+        <v>3.189631055854481</v>
       </c>
       <c r="K226" t="n">
-        <v>3.683213052336908</v>
+        <v>3.684605691622937</v>
       </c>
       <c r="L226" t="n">
-        <v>3.494066659128456</v>
+        <v>3.494066530474031</v>
       </c>
       <c r="M226" t="n">
-        <v>3.331673712150788</v>
+        <v>3.331460975645794</v>
       </c>
       <c r="N226" t="n">
-        <v>3.189631004691491</v>
+        <v>3.189708861061739</v>
       </c>
       <c r="O226" t="n">
-        <v>3.683068626938516</v>
+        <v>3.68306863319889</v>
       </c>
       <c r="P226" t="n">
-        <v>3.497141971060167</v>
+        <v>3.494208839840889</v>
       </c>
       <c r="Q226" t="n">
-        <v>3.331460917251726</v>
+        <v>3.331460921029499</v>
       </c>
       <c r="R226" t="n">
-        <v>3.1904901466538</v>
+        <v>3.18992249310639</v>
       </c>
       <c r="S226" t="n">
-        <v>3.68332579449417</v>
+        <v>3.683068705113341</v>
       </c>
       <c r="T226" t="n">
-        <v>3.494065694701422</v>
+        <v>3.49436717148623</v>
       </c>
       <c r="U226" t="n">
-        <v>3.331461058195181</v>
+        <v>3.33146092347253</v>
       </c>
       <c r="V226" t="n">
-        <v>3.189779764237538</v>
+        <v>3.189631001703529</v>
       </c>
       <c r="W226" t="n">
-        <v>3.686374284959742</v>
+        <v>3.683068630545914</v>
       </c>
       <c r="X226" t="n">
-        <v>3.494065714308679</v>
+        <v>3.496097645899638</v>
       </c>
       <c r="Y226" t="n">
-        <v>3.331460921410471</v>
+        <v>3.331461059210724</v>
       </c>
       <c r="Z226" t="n">
-        <v>3.189631054040644</v>
+        <v>3.189630994317722</v>
       </c>
     </row>
   </sheetData>
